--- a/doc/AUDIT_REGISTER_2026-08-04.xlsx
+++ b/doc/AUDIT_REGISTER_2026-08-04.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Register!$A$1:$H$206</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Register!$A$1:$H$212</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="556">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -83,33 +83,33 @@
     <t xml:space="preserve">Code, quick</t>
   </si>
   <si>
+    <t xml:space="preserve">Access tokens now carry `sid`; logout revokes the session from the TOKEN, not a body field the client never sent. Both issuance paths (login + refresh rotation) carry it — a test asserts every signAccessToken call site does. Response reports session_revoked honestly. Verified to FAIL 4/6 against the old service. Commit 809caad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC-C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No brute-force protection on any authentication endpoint; failed-login counter never enforced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limiters on all 11 credential surfaces across 3 tiers, AND the failed-login counter is now enforced as a decaying cooldown (migration 0495). 7 assertions on the curve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC-H1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The AI assistant executes business writes with no permission check at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code</t>
+  </si>
+  <si>
     <t xml:space="preserve">Open</t>
   </si>
   <si>
-    <t xml:space="preserve">app_user.controller.js:49 passes req.body.session_id || null; service.logout skips killSession when absent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC-C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No brute-force protection on any authentication endpoint; failed-login counter never enforced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limiters on all 11 credential surfaces across 3 tiers, AND the failed-login counter is now enforced as a decaying cooldown (migration 0495). 7 assertions on the curve.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC-H1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The AI assistant executes business writes with no permission check at all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Code</t>
-  </si>
-  <si>
     <t xml:space="preserve">As reported</t>
   </si>
   <si>
@@ -167,6 +167,9 @@
     <t xml:space="preserve">killSession has no ownership predicate</t>
   </si>
   <si>
+    <t xml:space="preserve">killSession is now always scoped to the acting user. Folded into the SEC-C2 fix. Commit 809caad.</t>
+  </si>
+  <si>
     <t xml:space="preserve">SEC-M3</t>
   </si>
   <si>
@@ -287,7 +290,7 @@
     <t xml:space="preserve">Asset depreciation never posts to the GL and records itself as posted</t>
   </si>
   <si>
-    <t xml:space="preserve">asset.service.js:73-82 uses 'account:' not 'account_code:', passes no sourceDocRef, catch swallows, markPosted sets posted=true. Identical bug fixed in payroll.service.js:149-151</t>
+    <t xml:space="preserve">Depreciation now reaches the GL: account_code + sourceDocRef, and a ledger rejection FAILS the call instead of setting posted=true with entry_id NULL. 11 assertions, verified to FAIL against the pre-fix file. Sweep found only asset+payroll; a grep-as-a-test blocks a third. Commit 62a9646. NOTE: existing bad rows need scripts/db/reconcile-depreciation.js.</t>
   </si>
   <si>
     <t xml:space="preserve">DI-5.1</t>
@@ -1022,7 +1025,7 @@
     <t xml:space="preserve">123 of 126 tables sort by an unindexed created_at - 462x speedup available</t>
   </si>
   <si>
-    <t xml:space="preserve">Zero 'ON ...(created_at' index declarations across 38 tenant migration files that reference created_at</t>
+    <t xml:space="preserve">Migration 0496 adds a created_at index to all 127 tenant tables that declare one (DDL-parsed: zero were indexed). Measured 462x. Plain CREATE INDEX because the migrator's multi-statement query is an implicit transaction block, where CONCURRENTLY cannot run. Targets verified against the DDL — but NOT YET EXECUTED. Commit 537a4af.</t>
   </si>
   <si>
     <t xml:space="preserve">PERF-S4</t>
@@ -1608,6 +1611,69 @@
   </si>
   <si>
     <t xml:space="preserve">Token pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dockerfile deps stage never copied packages/, so `@praxis/shared` (a file: dependency) could not be linked — the image had no invoicing module and every final_invoice route 404'd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer was cached from before the dep existed, so builds kept passing. Also a time bomb: the next package.json change would fail the build outright. Found by running the test suite. Commit 5ed5870.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scripts/deploy.sh git-pulls the repo containing itself, so bash keeps executing the OLD file — every change to it took effect one deploy late</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-existing. Surfaced when a fix to the backup step was pulled and the run failed with the exact bug it fixed. Now pulls then re-execs. Reproduced standalone. Commit cdc034d.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working tree is CRLF while every git blob is LF; a shell script edited on Windows becomes unparseable on the Linux server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rollback.sh failed with `syntax error near unexpected token $'do\r'` — the recovery script could not run at all. .gitattributes added; CI now asserts every tracked *.sh is LF and passes bash -n. Commit 54e3f2c.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">config/database.js is dead code in the API process — initDatabase() is defined and never called anywhere in src/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Its pool is permanently null, so query() always throws 'db pool not initialised'. Found because the first readiness probe used it and reported Postgres down on a healthy server. Consistent with DATA 4.1 (the RLS layer does not exist). Needs its own pass.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation rows already written with posted=true and entry_id NULL — the register reports accumulated depreciation the trial balance does not contain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data repair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage left by DI-5.5. Net book value understated; any asset disposed in the window computed gain/loss from the phantom figure. scripts/db/reconcile-depreciation.js finds and optionally clears the false flags (commit 1de3ab6). NOT YET RUN.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pino-pretty transport was spawned under NODE_ENV=test, leaking a worker thread per Jest process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caused 'A worker process has failed to exit gracefully'. Bought nothing — jest.setup.js already silences output. Pretty-printing is now development-only. Commit 5ed5870.</t>
   </si>
   <si>
     <t xml:space="preserve">Praxis LS - consolidated audit register, 2026-08-04</t>
@@ -2276,7 +2342,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H212"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
@@ -2357,25 +2423,25 @@
       <c r="E3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>19</v>
+      <c r="F3" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>11</v>
@@ -2390,27 +2456,27 @@
         <v>14</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>28</v>
@@ -2428,7 +2494,7 @@
         <v>30</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>18</v>
@@ -2454,13 +2520,13 @@
         <v>33</v>
       </c>
       <c r="D7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>28</v>
@@ -2478,13 +2544,13 @@
         <v>35</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="F8" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>28</v>
@@ -2502,7 +2568,7 @@
         <v>37</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>38</v>
@@ -2528,13 +2594,13 @@
         <v>41</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>28</v>
@@ -2555,10 +2621,10 @@
         <v>44</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>28</v>
@@ -2581,32 +2647,34 @@
       <c r="E12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="4"/>
+      <c r="F12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>28</v>
@@ -2615,22 +2683,22 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>28</v>
@@ -2639,22 +2707,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>28</v>
@@ -2663,22 +2731,22 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>28</v>
@@ -2687,22 +2755,22 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>28</v>
@@ -2711,74 +2779,74 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>28</v>
@@ -2787,22 +2855,22 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>28</v>
@@ -2811,22 +2879,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>28</v>
@@ -2835,19 +2903,19 @@
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>13</v>
@@ -2856,27 +2924,27 @@
         <v>14</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>28</v>
@@ -2885,22 +2953,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>28</v>
@@ -2909,13 +2977,13 @@
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>11</v>
@@ -2923,34 +2991,34 @@
       <c r="E26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>19</v>
+      <c r="F26" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>28</v>
@@ -2959,22 +3027,22 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>28</v>
@@ -2983,22 +3051,22 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>28</v>
@@ -3007,22 +3075,22 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>28</v>
@@ -3031,22 +3099,22 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>28</v>
@@ -3055,22 +3123,22 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>28</v>
@@ -3079,22 +3147,22 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>28</v>
@@ -3103,22 +3171,22 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>28</v>
@@ -3127,22 +3195,22 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>28</v>
@@ -3151,22 +3219,22 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>28</v>
@@ -3175,22 +3243,22 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>28</v>
@@ -3199,22 +3267,22 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>28</v>
@@ -3223,22 +3291,22 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="F39" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>28</v>
@@ -3247,22 +3315,22 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>28</v>
@@ -3271,48 +3339,48 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>28</v>
@@ -3321,22 +3389,22 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>28</v>
@@ -3345,22 +3413,22 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>28</v>
@@ -3369,22 +3437,22 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>28</v>
@@ -3393,22 +3461,22 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>28</v>
@@ -3417,22 +3485,22 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>28</v>
@@ -3441,22 +3509,22 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>28</v>
@@ -3465,22 +3533,22 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>28</v>
@@ -3489,22 +3557,22 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>28</v>
@@ -3513,22 +3581,22 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>28</v>
@@ -3537,22 +3605,22 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>28</v>
@@ -3561,22 +3629,22 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>28</v>
@@ -3585,22 +3653,22 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>28</v>
@@ -3609,22 +3677,22 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>28</v>
@@ -3633,22 +3701,22 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>28</v>
@@ -3657,22 +3725,22 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>28</v>
@@ -3681,22 +3749,22 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>28</v>
@@ -3705,19 +3773,19 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>13</v>
@@ -3726,24 +3794,24 @@
         <v>14</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>13</v>
@@ -3752,27 +3820,27 @@
         <v>14</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>28</v>
@@ -3781,13 +3849,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>11</v>
@@ -3796,7 +3864,7 @@
         <v>44</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>28</v>
@@ -3805,13 +3873,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>11</v>
@@ -3820,7 +3888,7 @@
         <v>44</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>28</v>
@@ -3829,22 +3897,22 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>28</v>
@@ -3853,19 +3921,19 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>13</v>
@@ -3874,18 +3942,18 @@
         <v>14</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>11</v>
@@ -3894,7 +3962,7 @@
         <v>44</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>28</v>
@@ -3903,19 +3971,19 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>13</v>
@@ -3924,18 +3992,18 @@
         <v>14</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>11</v>
@@ -3944,7 +4012,7 @@
         <v>44</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>28</v>
@@ -3953,22 +4021,22 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>28</v>
@@ -3977,22 +4045,22 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>28</v>
@@ -4001,13 +4069,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>11</v>
@@ -4022,24 +4090,24 @@
         <v>14</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>13</v>
@@ -4048,27 +4116,27 @@
         <v>14</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>28</v>
@@ -4077,22 +4145,22 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>28</v>
@@ -4101,19 +4169,19 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>13</v>
@@ -4122,24 +4190,24 @@
         <v>14</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>13</v>
@@ -4148,27 +4216,27 @@
         <v>14</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>28</v>
@@ -4177,22 +4245,22 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>28</v>
@@ -4201,19 +4269,19 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>13</v>
@@ -4222,27 +4290,27 @@
         <v>14</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>28</v>
@@ -4251,22 +4319,22 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>28</v>
@@ -4275,48 +4343,48 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>28</v>
@@ -4325,13 +4393,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>44</v>
@@ -4340,7 +4408,7 @@
         <v>44</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>28</v>
@@ -4349,22 +4417,22 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>28</v>
@@ -4373,22 +4441,22 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>28</v>
@@ -4397,22 +4465,22 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>28</v>
@@ -4421,13 +4489,13 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>44</v>
@@ -4436,7 +4504,7 @@
         <v>44</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>28</v>
@@ -4445,19 +4513,19 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>13</v>
@@ -4466,24 +4534,24 @@
         <v>14</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>13</v>
@@ -4492,24 +4560,24 @@
         <v>14</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>13</v>
@@ -4518,27 +4586,27 @@
         <v>14</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>28</v>
@@ -4547,13 +4615,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>11</v>
@@ -4568,27 +4636,27 @@
         <v>14</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>28</v>
@@ -4597,22 +4665,22 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>28</v>
@@ -4621,22 +4689,22 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D96" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="F96" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>28</v>
@@ -4645,22 +4713,22 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D97" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="F97" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>28</v>
@@ -4669,19 +4737,19 @@
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>13</v>
@@ -4690,27 +4758,27 @@
         <v>14</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>28</v>
@@ -4719,22 +4787,22 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>28</v>
@@ -4743,48 +4811,48 @@
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G101" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>28</v>
@@ -4793,22 +4861,22 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G103" s="4" t="s">
         <v>28</v>
@@ -4817,22 +4885,22 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>28</v>
@@ -4841,22 +4909,22 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G105" s="4" t="s">
         <v>28</v>
@@ -4865,22 +4933,22 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G106" s="4" t="s">
         <v>28</v>
@@ -4889,22 +4957,22 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G107" s="4" t="s">
         <v>28</v>
@@ -4913,22 +4981,22 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D108" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G108" s="4" t="s">
         <v>28</v>
@@ -4937,22 +5005,22 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>28</v>
@@ -4961,22 +5029,22 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G110" s="4" t="s">
         <v>28</v>
@@ -4985,22 +5053,22 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G111" s="4" t="s">
         <v>28</v>
@@ -5009,22 +5077,22 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>28</v>
@@ -5033,22 +5101,22 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>28</v>
@@ -5057,22 +5125,22 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G114" s="4" t="s">
         <v>28</v>
@@ -5081,22 +5149,22 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G115" s="4" t="s">
         <v>28</v>
@@ -5105,22 +5173,22 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G116" s="4" t="s">
         <v>28</v>
@@ -5129,22 +5197,22 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G117" s="4" t="s">
         <v>28</v>
@@ -5153,22 +5221,22 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>28</v>
@@ -5177,22 +5245,22 @@
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>28</v>
@@ -5201,48 +5269,48 @@
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G120" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G121" s="4" t="s">
         <v>28</v>
@@ -5251,48 +5319,48 @@
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>19</v>
+        <v>176</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="G122" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G123" s="4" t="s">
         <v>28</v>
@@ -5301,22 +5369,22 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G124" s="4" t="s">
         <v>28</v>
@@ -5325,22 +5393,22 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>28</v>
@@ -5349,22 +5417,22 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G126" s="4" t="s">
         <v>28</v>
@@ -5373,22 +5441,22 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>28</v>
@@ -5397,22 +5465,22 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G128" s="4" t="s">
         <v>28</v>
@@ -5421,22 +5489,22 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>28</v>
@@ -5445,22 +5513,22 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G130" s="4" t="s">
         <v>28</v>
@@ -5469,22 +5537,22 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>28</v>
@@ -5493,22 +5561,22 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>28</v>
@@ -5517,22 +5585,22 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>28</v>
@@ -5541,22 +5609,22 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>28</v>
@@ -5565,22 +5633,22 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D135" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>28</v>
@@ -5589,22 +5657,22 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D136" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>28</v>
@@ -5613,22 +5681,22 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D137" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>28</v>
@@ -5637,22 +5705,22 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>28</v>
@@ -5661,22 +5729,22 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>28</v>
@@ -5685,22 +5753,22 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>28</v>
@@ -5709,22 +5777,22 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>28</v>
@@ -5733,22 +5801,22 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>28</v>
@@ -5757,22 +5825,22 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>28</v>
@@ -5781,19 +5849,19 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>13</v>
@@ -5802,24 +5870,24 @@
         <v>14</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>13</v>
@@ -5828,27 +5896,27 @@
         <v>14</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>28</v>
@@ -5857,22 +5925,22 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>28</v>
@@ -5881,22 +5949,22 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>28</v>
@@ -5905,22 +5973,22 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>28</v>
@@ -5929,22 +5997,22 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>28</v>
@@ -5953,22 +6021,22 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>28</v>
@@ -5977,22 +6045,22 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G152" s="4" t="s">
         <v>28</v>
@@ -6001,22 +6069,22 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G153" s="4" t="s">
         <v>28</v>
@@ -6025,22 +6093,22 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G154" s="4" t="s">
         <v>28</v>
@@ -6049,22 +6117,22 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>28</v>
@@ -6073,22 +6141,22 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>28</v>
@@ -6097,22 +6165,22 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>28</v>
@@ -6121,22 +6189,22 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G158" s="4" t="s">
         <v>28</v>
@@ -6145,22 +6213,22 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>28</v>
@@ -6169,19 +6237,19 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>13</v>
@@ -6190,27 +6258,27 @@
         <v>14</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>28</v>
@@ -6219,22 +6287,22 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>28</v>
@@ -6243,22 +6311,22 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>28</v>
@@ -6267,19 +6335,19 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>13</v>
@@ -6288,27 +6356,27 @@
         <v>14</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>28</v>
@@ -6317,48 +6385,48 @@
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D166" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D167" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>28</v>
@@ -6367,22 +6435,22 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D168" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>28</v>
@@ -6391,22 +6459,22 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D169" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>28</v>
@@ -6415,22 +6483,22 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D170" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G170" s="4" t="s">
         <v>28</v>
@@ -6439,19 +6507,19 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D171" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>13</v>
@@ -6460,27 +6528,27 @@
         <v>14</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>28</v>
@@ -6489,22 +6557,22 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D173" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>28</v>
@@ -6513,22 +6581,22 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D174" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>28</v>
@@ -6537,22 +6605,22 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D175" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G175" s="4" t="s">
         <v>28</v>
@@ -6561,22 +6629,22 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G176" s="4" t="s">
         <v>28</v>
@@ -6585,19 +6653,19 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D177" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>13</v>
@@ -6606,27 +6674,27 @@
         <v>14</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D178" s="13" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>28</v>
@@ -6635,22 +6703,22 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D179" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>28</v>
@@ -6659,22 +6727,22 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>28</v>
@@ -6683,22 +6751,22 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>28</v>
@@ -6707,22 +6775,22 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>28</v>
@@ -6731,22 +6799,22 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D183" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>28</v>
@@ -6755,22 +6823,22 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D184" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>28</v>
@@ -6779,22 +6847,22 @@
     </row>
     <row r="185" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D185" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>28</v>
@@ -6803,22 +6871,22 @@
     </row>
     <row r="186" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D186" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>28</v>
@@ -6827,22 +6895,22 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>28</v>
@@ -6851,74 +6919,74 @@
     </row>
     <row r="188" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G188" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F189" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G189" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G190" s="4" t="s">
         <v>28</v>
@@ -6927,22 +6995,22 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G191" s="4" t="s">
         <v>28</v>
@@ -6951,48 +7019,48 @@
     </row>
     <row r="192" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G193" s="4" t="s">
         <v>28</v>
@@ -7001,22 +7069,22 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G194" s="4" t="s">
         <v>28</v>
@@ -7025,22 +7093,22 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G195" s="4" t="s">
         <v>28</v>
@@ -7049,22 +7117,22 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G196" s="4" t="s">
         <v>28</v>
@@ -7073,22 +7141,22 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G197" s="4" t="s">
         <v>28</v>
@@ -7097,22 +7165,22 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D198" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E198" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E198" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="F198" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G198" s="4" t="s">
         <v>28</v>
@@ -7121,48 +7189,48 @@
     </row>
     <row r="199" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D199" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F199" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G199" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D200" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>28</v>
@@ -7171,22 +7239,22 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D201" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>28</v>
@@ -7195,22 +7263,22 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D202" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G202" s="4" t="s">
         <v>28</v>
@@ -7219,22 +7287,22 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D203" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G203" s="4" t="s">
         <v>28</v>
@@ -7243,22 +7311,22 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D204" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G204" s="4" t="s">
         <v>28</v>
@@ -7267,22 +7335,22 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D205" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G205" s="4" t="s">
         <v>28</v>
@@ -7291,30 +7359,186 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D206" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H206" s="4"/>
     </row>
+    <row r="207" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F207" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G207" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H207" s="4" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G208" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H208" s="4" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F209" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G209" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H209" s="4" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="D210" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E210" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G210" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H210" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G211" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H211" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="D212" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G212" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>549</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H206"/>
+  <autoFilter ref="A1:H212"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F206" type="list">
       <formula1>"Open,In progress,Partially fixed,Largely fixed,Fixed,Closed,Won't fix,Deferred"</formula1>
@@ -7346,7 +7570,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>528</v>
+        <v>550</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -7358,7 +7582,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>529</v>
+        <v>551</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -7386,22 +7610,22 @@
         <v>11</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>44</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>530</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7439,7 +7663,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A6,Register!$D$2:$D$206,B$4)</f>
@@ -7472,7 +7696,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A7,Register!$D$2:$D$206,B$4)</f>
@@ -7505,7 +7729,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,B$4)</f>
@@ -7538,7 +7762,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,B$4)</f>
@@ -7571,7 +7795,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,B$4)</f>
@@ -7604,7 +7828,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,B$4)</f>
@@ -7637,7 +7861,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>530</v>
+        <v>552</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -7680,7 +7904,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>531</v>
+        <v>553</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -7692,11 +7916,11 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B15" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A15)</f>
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -7707,7 +7931,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A16)</f>
@@ -7726,7 +7950,7 @@
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,"Fixed")</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -7737,7 +7961,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A18)</f>
@@ -7752,7 +7976,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A19)</f>
@@ -7767,11 +7991,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>533</v>
+        <v>555</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">COUNTIF(Register!$G$2:$G$206,"Verified in code")</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>

--- a/doc/AUDIT_REGISTER_2026-08-04.xlsx
+++ b/doc/AUDIT_REGISTER_2026-08-04.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="558">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -587,10 +587,16 @@
     <t xml:space="preserve">No centralised error tracking of any kind</t>
   </si>
   <si>
+    <t xml:space="preserve">shared/observability/error-reporter.js — every 5xx, uncaughtException and unhandledRejection reports with tenant/user/request_id/route/build. Dedupe + id normalisation + frame-drift stability + 20/min ceiling so the channel stays usable. 4xx and ZodError never reported. Commit e78a566.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-E2</t>
   </si>
   <si>
     <t xml:space="preserve">Frontend errors are completely invisible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /api/client-errors + client/src/lib/error-reporting.ts covering render, window 'error' and unhandledrejection. ErrorBoundary's dead onError hook now reports by default. sendBeacon survives the post-crash reload. Commit e78a566.</t>
   </si>
   <si>
     <t xml:space="preserve">OBS-L1</t>
@@ -3887,23 +3893,25 @@
       <c r="E63" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H63" s="4"/>
+      <c r="F63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>11</v>
@@ -3911,23 +3919,25 @@
       <c r="E64" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H64" s="4"/>
+      <c r="F64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>11</v>
@@ -3942,18 +3952,18 @@
         <v>14</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>11</v>
@@ -3971,13 +3981,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>11</v>
@@ -3992,18 +4002,18 @@
         <v>14</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>11</v>
@@ -4021,19 +4031,19 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>27</v>
@@ -4045,19 +4055,19 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>27</v>
@@ -4069,13 +4079,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>11</v>
@@ -4090,18 +4100,18 @@
         <v>14</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>25</v>
@@ -4116,18 +4126,18 @@
         <v>14</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>25</v>
@@ -4145,19 +4155,19 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>27</v>
@@ -4169,13 +4179,13 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>25</v>
@@ -4190,18 +4200,18 @@
         <v>14</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>25</v>
@@ -4216,24 +4226,24 @@
         <v>14</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>27</v>
@@ -4245,13 +4255,13 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>25</v>
@@ -4269,13 +4279,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>25</v>
@@ -4290,18 +4300,18 @@
         <v>14</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>25</v>
@@ -4319,13 +4329,13 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>25</v>
@@ -4343,13 +4353,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>25</v>
@@ -4364,24 +4374,24 @@
         <v>28</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>27</v>
@@ -4393,13 +4403,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>44</v>
@@ -4417,13 +4427,13 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>44</v>
@@ -4441,13 +4451,13 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>44</v>
@@ -4465,13 +4475,13 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>44</v>
@@ -4489,13 +4499,13 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>44</v>
@@ -4513,13 +4523,13 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>44</v>
@@ -4534,24 +4544,24 @@
         <v>14</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>13</v>
@@ -4560,24 +4570,24 @@
         <v>14</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>13</v>
@@ -4586,18 +4596,18 @@
         <v>14</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>11</v>
@@ -4615,13 +4625,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>11</v>
@@ -4636,24 +4646,24 @@
         <v>14</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>27</v>
@@ -4665,19 +4675,19 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>27</v>
@@ -4689,13 +4699,13 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>25</v>
@@ -4713,13 +4723,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>25</v>
@@ -4737,19 +4747,19 @@
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>13</v>
@@ -4758,24 +4768,24 @@
         <v>14</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>27</v>
@@ -4787,19 +4797,19 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>27</v>
@@ -4811,19 +4821,19 @@
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>130</v>
@@ -4832,24 +4842,24 @@
         <v>14</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>27</v>
@@ -4861,13 +4871,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>44</v>
@@ -4885,13 +4895,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>44</v>
@@ -4909,19 +4919,19 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>27</v>
@@ -4933,19 +4943,19 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>27</v>
@@ -4957,19 +4967,19 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>27</v>
@@ -4981,19 +4991,19 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D108" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>27</v>
@@ -5005,19 +5015,19 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>27</v>
@@ -5029,19 +5039,19 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>27</v>
@@ -5053,13 +5063,13 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>44</v>
@@ -5077,19 +5087,19 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>27</v>
@@ -5101,19 +5111,19 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>27</v>
@@ -5125,19 +5135,19 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>27</v>
@@ -5149,19 +5159,19 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>27</v>
@@ -5173,19 +5183,19 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>27</v>
@@ -5197,19 +5207,19 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>27</v>
@@ -5221,19 +5231,19 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>27</v>
@@ -5245,22 +5255,22 @@
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>28</v>
@@ -5269,13 +5279,13 @@
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>11</v>
@@ -5290,18 +5300,18 @@
         <v>14</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>11</v>
@@ -5319,13 +5329,13 @@
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>11</v>
@@ -5340,24 +5350,24 @@
         <v>14</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>27</v>
@@ -5369,13 +5379,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D124" s="8" t="s">
         <v>25</v>
@@ -5393,13 +5403,13 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>25</v>
@@ -5417,13 +5427,13 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D126" s="8" t="s">
         <v>25</v>
@@ -5441,13 +5451,13 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D127" s="8" t="s">
         <v>25</v>
@@ -5465,13 +5475,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>25</v>
@@ -5489,13 +5499,13 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D129" s="8" t="s">
         <v>25</v>
@@ -5513,13 +5523,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D130" s="8" t="s">
         <v>25</v>
@@ -5537,13 +5547,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D131" s="8" t="s">
         <v>25</v>
@@ -5561,13 +5571,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>44</v>
@@ -5585,13 +5595,13 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>44</v>
@@ -5609,13 +5619,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>44</v>
@@ -5633,13 +5643,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D135" s="9" t="s">
         <v>44</v>
@@ -5657,19 +5667,19 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D136" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>27</v>
@@ -5681,13 +5691,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D137" s="9" t="s">
         <v>44</v>
@@ -5705,13 +5715,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>69</v>
@@ -5729,13 +5739,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D139" s="10" t="s">
         <v>69</v>
@@ -5753,19 +5763,19 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>27</v>
@@ -5777,19 +5787,19 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B141" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="B141" s="4" t="s">
-        <v>371</v>
-      </c>
       <c r="C141" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>27</v>
@@ -5801,19 +5811,19 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>27</v>
@@ -5825,19 +5835,19 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>27</v>
@@ -5849,19 +5859,19 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>13</v>
@@ -5870,24 +5880,24 @@
         <v>14</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>13</v>
@@ -5896,24 +5906,24 @@
         <v>14</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>27</v>
@@ -5925,19 +5935,19 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D147" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>27</v>
@@ -5949,19 +5959,19 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D148" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>27</v>
@@ -5973,19 +5983,19 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D149" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>27</v>
@@ -5997,19 +6007,19 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>27</v>
@@ -6021,19 +6031,19 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D151" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>27</v>
@@ -6045,19 +6055,19 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D152" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>27</v>
@@ -6069,19 +6079,19 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>27</v>
@@ -6093,19 +6103,19 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>27</v>
@@ -6117,19 +6127,19 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>27</v>
@@ -6141,19 +6151,19 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>27</v>
@@ -6165,19 +6175,19 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>27</v>
@@ -6189,19 +6199,19 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D158" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>27</v>
@@ -6213,19 +6223,19 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D159" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>27</v>
@@ -6237,19 +6247,19 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D160" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>13</v>
@@ -6258,24 +6268,24 @@
         <v>14</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D161" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>27</v>
@@ -6287,19 +6297,19 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D162" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>27</v>
@@ -6311,19 +6321,19 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D163" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>27</v>
@@ -6335,19 +6345,19 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>13</v>
@@ -6356,24 +6366,24 @@
         <v>14</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D165" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>27</v>
@@ -6385,45 +6395,45 @@
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D166" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D167" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>27</v>
@@ -6435,19 +6445,19 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D168" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>27</v>
@@ -6459,19 +6469,19 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D169" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>27</v>
@@ -6483,19 +6493,19 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D170" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>27</v>
@@ -6507,19 +6517,19 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D171" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>13</v>
@@ -6528,24 +6538,24 @@
         <v>14</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>27</v>
@@ -6557,19 +6567,19 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D173" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>27</v>
@@ -6581,19 +6591,19 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D174" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>27</v>
@@ -6605,19 +6615,19 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D175" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>27</v>
@@ -6629,19 +6639,19 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>27</v>
@@ -6653,19 +6663,19 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D177" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>13</v>
@@ -6674,24 +6684,24 @@
         <v>14</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D178" s="13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>27</v>
@@ -6703,19 +6713,19 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D179" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>27</v>
@@ -6727,19 +6737,19 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>27</v>
@@ -6751,19 +6761,19 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="D181" s="14" t="s">
         <v>468</v>
       </c>
-      <c r="B181" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="D181" s="14" t="s">
-        <v>466</v>
-      </c>
       <c r="E181" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>27</v>
@@ -6775,19 +6785,19 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>27</v>
@@ -6799,19 +6809,19 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D183" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>27</v>
@@ -6823,19 +6833,19 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D184" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F184" s="4" t="s">
         <v>27</v>
@@ -6847,22 +6857,22 @@
     </row>
     <row r="185" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D185" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>28</v>
@@ -6871,22 +6881,22 @@
     </row>
     <row r="186" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D186" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>28</v>
@@ -6895,13 +6905,13 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>11</v>
@@ -6919,13 +6929,13 @@
     </row>
     <row r="188" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B188" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="B188" s="4" t="s">
-        <v>481</v>
-      </c>
       <c r="C188" s="4" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>11</v>
@@ -6940,24 +6950,24 @@
         <v>14</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F189" s="11" t="s">
         <v>130</v>
@@ -6966,24 +6976,24 @@
         <v>14</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F190" s="4" t="s">
         <v>27</v>
@@ -6995,13 +7005,13 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>11</v>
@@ -7019,45 +7029,45 @@
     </row>
     <row r="192" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D192" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D193" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F193" s="4" t="s">
         <v>27</v>
@@ -7069,13 +7079,13 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D194" s="8" t="s">
         <v>25</v>
@@ -7093,19 +7103,19 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>27</v>
@@ -7117,13 +7127,13 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D196" s="8" t="s">
         <v>25</v>
@@ -7141,19 +7151,19 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>27</v>
@@ -7165,13 +7175,13 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>25</v>
@@ -7189,13 +7199,13 @@
     </row>
     <row r="199" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D199" s="9" t="s">
         <v>44</v>
@@ -7210,24 +7220,24 @@
         <v>14</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D200" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>27</v>
@@ -7239,19 +7249,19 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D201" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>27</v>
@@ -7263,19 +7273,19 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D202" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>27</v>
@@ -7287,13 +7297,13 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D203" s="9" t="s">
         <v>44</v>
@@ -7311,19 +7321,19 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D204" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>27</v>
@@ -7335,13 +7345,13 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D205" s="9" t="s">
         <v>44</v>
@@ -7359,19 +7369,19 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D206" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>27</v>
@@ -7381,21 +7391,21 @@
       </c>
       <c r="H206" s="4"/>
     </row>
-    <row r="207" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>13</v>
@@ -7404,24 +7414,24 @@
         <v>14</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>13</v>
@@ -7430,18 +7440,18 @@
         <v>14</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D209" s="5" t="s">
         <v>11</v>
@@ -7456,18 +7466,18 @@
         <v>14</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D210" s="8" t="s">
         <v>25</v>
@@ -7482,24 +7492,24 @@
         <v>14</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>27</v>
@@ -7508,18 +7518,18 @@
         <v>14</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="212" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D212" s="10" t="s">
         <v>69</v>
@@ -7534,7 +7544,7 @@
         <v>14</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -7570,7 +7580,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -7582,7 +7592,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -7613,19 +7623,19 @@
         <v>25</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>44</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7729,7 +7739,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,B$4)</f>
@@ -7762,7 +7772,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,B$4)</f>
@@ -7795,7 +7805,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,B$4)</f>
@@ -7828,7 +7838,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,B$4)</f>
@@ -7861,7 +7871,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -7904,7 +7914,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -7920,7 +7930,7 @@
       </c>
       <c r="B15" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A15)</f>
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -7950,7 +7960,7 @@
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,"Fixed")</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -7961,7 +7971,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A18)</f>
@@ -7976,7 +7986,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A19)</f>
@@ -7991,11 +8001,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">COUNTIF(Register!$G$2:$G$206,"Verified in code")</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>

--- a/doc/AUDIT_REGISTER_2026-08-04.xlsx
+++ b/doc/AUDIT_REGISTER_2026-08-04.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="559">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -579,6 +579,9 @@
   </si>
   <si>
     <t xml:space="preserve">Dead-lettered business events are a silent black hole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEAD is now distinguishable from FAILED (error + report vs warn), countDeadLetters() is the query that never existed, the worker sweep runs a census every pass and notifies on a new death then daily while a backlog stands, and /api/health/ready exposes dead_letters per tenant (degraded, not 503 — dropped events are a business failure, not a deploy blocker). 17 assertions incl. 'a retriable failure must NOT notify' and 'a census failure must not fail the drain'.</t>
   </si>
   <si>
     <t xml:space="preserve">OBS-E1</t>
@@ -3869,23 +3872,25 @@
       <c r="E62" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H62" s="4"/>
+      <c r="F62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>11</v>
@@ -3900,18 +3905,18 @@
         <v>14</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>11</v>
@@ -3926,18 +3931,18 @@
         <v>14</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>11</v>
@@ -3952,18 +3957,18 @@
         <v>14</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>11</v>
@@ -3981,13 +3986,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>11</v>
@@ -4002,18 +4007,18 @@
         <v>14</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>11</v>
@@ -4031,19 +4036,19 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>27</v>
@@ -4055,19 +4060,19 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>27</v>
@@ -4079,13 +4084,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>11</v>
@@ -4100,18 +4105,18 @@
         <v>14</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>25</v>
@@ -4126,18 +4131,18 @@
         <v>14</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>25</v>
@@ -4155,19 +4160,19 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>27</v>
@@ -4179,13 +4184,13 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>25</v>
@@ -4200,18 +4205,18 @@
         <v>14</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>25</v>
@@ -4226,24 +4231,24 @@
         <v>14</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>27</v>
@@ -4255,13 +4260,13 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>25</v>
@@ -4279,13 +4284,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>25</v>
@@ -4300,18 +4305,18 @@
         <v>14</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>25</v>
@@ -4329,13 +4334,13 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>25</v>
@@ -4353,13 +4358,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>25</v>
@@ -4374,24 +4379,24 @@
         <v>28</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>27</v>
@@ -4403,13 +4408,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>44</v>
@@ -4427,13 +4432,13 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>44</v>
@@ -4451,13 +4456,13 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>44</v>
@@ -4475,13 +4480,13 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>44</v>
@@ -4499,13 +4504,13 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>44</v>
@@ -4523,13 +4528,13 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>44</v>
@@ -4544,24 +4549,24 @@
         <v>14</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>13</v>
@@ -4570,24 +4575,24 @@
         <v>14</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>13</v>
@@ -4596,18 +4601,18 @@
         <v>14</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>11</v>
@@ -4625,13 +4630,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>11</v>
@@ -4646,24 +4651,24 @@
         <v>14</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>27</v>
@@ -4675,19 +4680,19 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>27</v>
@@ -4699,13 +4704,13 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>25</v>
@@ -4723,13 +4728,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>25</v>
@@ -4747,19 +4752,19 @@
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>13</v>
@@ -4768,24 +4773,24 @@
         <v>14</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>27</v>
@@ -4797,19 +4802,19 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>27</v>
@@ -4821,19 +4826,19 @@
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>130</v>
@@ -4842,24 +4847,24 @@
         <v>14</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>27</v>
@@ -4871,13 +4876,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>44</v>
@@ -4895,13 +4900,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>44</v>
@@ -4919,19 +4924,19 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>27</v>
@@ -4943,19 +4948,19 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>27</v>
@@ -4967,19 +4972,19 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>27</v>
@@ -4991,19 +4996,19 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D108" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>27</v>
@@ -5015,19 +5020,19 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>27</v>
@@ -5039,19 +5044,19 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>27</v>
@@ -5063,13 +5068,13 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>44</v>
@@ -5087,19 +5092,19 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>27</v>
@@ -5111,19 +5116,19 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>27</v>
@@ -5135,19 +5140,19 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>27</v>
@@ -5159,19 +5164,19 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>27</v>
@@ -5183,19 +5188,19 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>27</v>
@@ -5207,19 +5212,19 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>27</v>
@@ -5231,19 +5236,19 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>27</v>
@@ -5255,22 +5260,22 @@
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>28</v>
@@ -5279,13 +5284,13 @@
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>11</v>
@@ -5300,18 +5305,18 @@
         <v>14</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>11</v>
@@ -5329,13 +5334,13 @@
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>11</v>
@@ -5350,24 +5355,24 @@
         <v>14</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>27</v>
@@ -5379,13 +5384,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D124" s="8" t="s">
         <v>25</v>
@@ -5403,13 +5408,13 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>25</v>
@@ -5427,13 +5432,13 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D126" s="8" t="s">
         <v>25</v>
@@ -5451,13 +5456,13 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D127" s="8" t="s">
         <v>25</v>
@@ -5475,13 +5480,13 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>25</v>
@@ -5499,13 +5504,13 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D129" s="8" t="s">
         <v>25</v>
@@ -5523,13 +5528,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D130" s="8" t="s">
         <v>25</v>
@@ -5547,13 +5552,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D131" s="8" t="s">
         <v>25</v>
@@ -5571,13 +5576,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>44</v>
@@ -5595,13 +5600,13 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>44</v>
@@ -5619,13 +5624,13 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>44</v>
@@ -5643,13 +5648,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D135" s="9" t="s">
         <v>44</v>
@@ -5667,19 +5672,19 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D136" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>27</v>
@@ -5691,13 +5696,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D137" s="9" t="s">
         <v>44</v>
@@ -5715,13 +5720,13 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>69</v>
@@ -5739,13 +5744,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D139" s="10" t="s">
         <v>69</v>
@@ -5763,19 +5768,19 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>27</v>
@@ -5787,19 +5792,19 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>27</v>
@@ -5811,19 +5816,19 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>27</v>
@@ -5835,19 +5840,19 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>27</v>
@@ -5859,19 +5864,19 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>13</v>
@@ -5880,24 +5885,24 @@
         <v>14</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>13</v>
@@ -5906,24 +5911,24 @@
         <v>14</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>27</v>
@@ -5935,19 +5940,19 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D147" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>27</v>
@@ -5959,19 +5964,19 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D148" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>27</v>
@@ -5983,19 +5988,19 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D149" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>27</v>
@@ -6007,19 +6012,19 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>27</v>
@@ -6031,19 +6036,19 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D151" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>27</v>
@@ -6055,19 +6060,19 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D152" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>27</v>
@@ -6079,19 +6084,19 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>27</v>
@@ -6103,19 +6108,19 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>27</v>
@@ -6127,19 +6132,19 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>27</v>
@@ -6151,19 +6156,19 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>27</v>
@@ -6175,19 +6180,19 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>27</v>
@@ -6199,19 +6204,19 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D158" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>27</v>
@@ -6223,19 +6228,19 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D159" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>27</v>
@@ -6247,19 +6252,19 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D160" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>13</v>
@@ -6268,24 +6273,24 @@
         <v>14</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D161" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>27</v>
@@ -6297,19 +6302,19 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D162" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>27</v>
@@ -6321,19 +6326,19 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D163" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>27</v>
@@ -6345,19 +6350,19 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>13</v>
@@ -6366,24 +6371,24 @@
         <v>14</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D165" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>27</v>
@@ -6395,45 +6400,45 @@
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D166" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D167" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>27</v>
@@ -6445,19 +6450,19 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D168" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>27</v>
@@ -6469,19 +6474,19 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D169" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>27</v>
@@ -6493,19 +6498,19 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D170" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>27</v>
@@ -6517,19 +6522,19 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D171" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>13</v>
@@ -6538,24 +6543,24 @@
         <v>14</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>27</v>
@@ -6567,19 +6572,19 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D173" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>27</v>
@@ -6591,19 +6596,19 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D174" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>27</v>
@@ -6615,19 +6620,19 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D175" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>27</v>
@@ -6639,19 +6644,19 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>27</v>
@@ -6663,19 +6668,19 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D177" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>13</v>
@@ -6684,24 +6689,24 @@
         <v>14</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D178" s="13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>27</v>
@@ -6713,19 +6718,19 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D179" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>27</v>
@@ -6737,19 +6742,19 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>27</v>
@@ -6761,19 +6766,19 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>27</v>
@@ -6785,19 +6790,19 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>27</v>
@@ -6809,19 +6814,19 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D183" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>27</v>
@@ -6833,19 +6838,19 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D184" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F184" s="4" t="s">
         <v>27</v>
@@ -6857,22 +6862,22 @@
     </row>
     <row r="185" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D185" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>28</v>
@@ -6881,22 +6886,22 @@
     </row>
     <row r="186" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D186" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>28</v>
@@ -6905,13 +6910,13 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>11</v>
@@ -6929,13 +6934,13 @@
     </row>
     <row r="188" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>11</v>
@@ -6950,24 +6955,24 @@
         <v>14</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F189" s="11" t="s">
         <v>130</v>
@@ -6976,24 +6981,24 @@
         <v>14</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F190" s="4" t="s">
         <v>27</v>
@@ -7005,13 +7010,13 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>11</v>
@@ -7029,45 +7034,45 @@
     </row>
     <row r="192" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D192" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D193" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F193" s="4" t="s">
         <v>27</v>
@@ -7079,13 +7084,13 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D194" s="8" t="s">
         <v>25</v>
@@ -7103,19 +7108,19 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>27</v>
@@ -7127,13 +7132,13 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D196" s="8" t="s">
         <v>25</v>
@@ -7151,19 +7156,19 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>27</v>
@@ -7175,13 +7180,13 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>25</v>
@@ -7199,13 +7204,13 @@
     </row>
     <row r="199" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D199" s="9" t="s">
         <v>44</v>
@@ -7220,24 +7225,24 @@
         <v>14</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D200" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>27</v>
@@ -7249,19 +7254,19 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D201" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>27</v>
@@ -7273,19 +7278,19 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D202" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>27</v>
@@ -7297,13 +7302,13 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D203" s="9" t="s">
         <v>44</v>
@@ -7321,19 +7326,19 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D204" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>27</v>
@@ -7345,13 +7350,13 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D205" s="9" t="s">
         <v>44</v>
@@ -7369,19 +7374,19 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D206" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>27</v>
@@ -7393,19 +7398,19 @@
     </row>
     <row r="207" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>13</v>
@@ -7414,24 +7419,24 @@
         <v>14</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>13</v>
@@ -7440,18 +7445,18 @@
         <v>14</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D209" s="5" t="s">
         <v>11</v>
@@ -7466,18 +7471,18 @@
         <v>14</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D210" s="8" t="s">
         <v>25</v>
@@ -7492,24 +7497,24 @@
         <v>14</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>27</v>
@@ -7518,18 +7523,18 @@
         <v>14</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B212" s="4" t="s">
         <v>174</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D212" s="10" t="s">
         <v>69</v>
@@ -7544,7 +7549,7 @@
         <v>14</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -7580,7 +7585,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -7592,7 +7597,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -7623,19 +7628,19 @@
         <v>25</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>44</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7739,7 +7744,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,B$4)</f>
@@ -7772,7 +7777,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,B$4)</f>
@@ -7805,7 +7810,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,B$4)</f>
@@ -7838,7 +7843,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,B$4)</f>
@@ -7871,7 +7876,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -7914,7 +7919,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -7930,7 +7935,7 @@
       </c>
       <c r="B15" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A15)</f>
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -7960,7 +7965,7 @@
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,"Fixed")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -7971,7 +7976,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A18)</f>
@@ -7986,7 +7991,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A19)</f>
@@ -8001,11 +8006,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">COUNTIF(Register!$G$2:$G$206,"Verified in code")</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>

--- a/doc/AUDIT_REGISTER_2026-08-04.xlsx
+++ b/doc/AUDIT_REGISTER_2026-08-04.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="570">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -281,6 +281,9 @@
     <t xml:space="preserve">Delete</t>
   </si>
   <si>
+    <t xml:space="preserve">src/middleware/audit.js deleted — never imported or mounted, so it read as an active control during review.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-5.5</t>
   </si>
   <si>
@@ -575,6 +578,9 @@
     <t xml:space="preserve">Redis outage boots the app silently degraded</t>
   </si>
   <si>
+    <t xml:space="preserve">Redis boot failure is now ERROR + a fatal report naming exactly what degrades (sessions, rate limiting, identity cache, socket.io pub-sub, ALL job enqueueing), and readiness reports it. Still non-fatal — refusing to boot would turn a degraded cache into a total outage.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-A6</t>
   </si>
   <si>
@@ -632,6 +638,9 @@
     <t xml:space="preserve">No metrics of any kind, no dashboard, no baseline</t>
   </si>
   <si>
+    <t xml:space="preserve">shared/observability/metrics.js + GET /api/metrics (Prometheus text). HTTP/db/job/auth/rbac counters and duration histograms. Hand-rolled, no new dependency; routes templated so uuids cannot explode cardinality. METRICS_TOKEN guards it when set.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-T1</t>
   </si>
   <si>
@@ -674,6 +683,9 @@
     <t xml:space="preserve">The worker is entirely unmonitored</t>
   </si>
   <si>
+    <t xml:space="preserve">Worker job start/done now timed, per-queue duration histogram, completed/failed counters and worker-error counter. Liveness is a fact rather than an assumption.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-E3</t>
   </si>
   <si>
@@ -683,6 +695,9 @@
     <t xml:space="preserve">Quick / Medium</t>
   </si>
   <si>
+    <t xml:space="preserve">request_id is put into AsyncLocalStorage by tenant-context, emitted on every log line by the mixin, and stamped onto enqueued job payloads. Minted-then-discarded is fixed end to end.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-E4</t>
   </si>
   <si>
@@ -707,6 +722,9 @@
     <t xml:space="preserve">Logs are neither durable nor shipped; lost on every deploy</t>
   </si>
   <si>
+    <t xml:space="preserve">Rotation half: json-file capped at 50m x5 on all five services — unbounded growth on an unmonitored disk was a plausible CAUSE of an outage. Shipping off-box remains open.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-M2</t>
   </si>
   <si>
@@ -719,7 +737,7 @@
     <t xml:space="preserve">No timing recorded anywhere</t>
   </si>
   <si>
-    <t xml:space="preserve">Response time on every access-log line.</t>
+    <t xml:space="preserve">HTTP duration histogram in the access-log middleware; job duration measured in workers.js (start/done were logged with elapsed never computed); db query duration on both query paths.</t>
   </si>
   <si>
     <t xml:space="preserve">OBS-T4</t>
@@ -728,6 +746,9 @@
     <t xml:space="preserve">Auth, RBAC and tenant middleware log nothing</t>
   </si>
   <si>
+    <t xml:space="preserve">auth.js and rbac.js had ZERO logger calls. Failed authentication and permission denial are now logged and counted (praxis_auth_failures_total, praxis_rbac_denials_total) — a debugging gap and a credential-stuffing detection gap.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-I3</t>
   </si>
   <si>
@@ -758,6 +779,9 @@
     <t xml:space="preserve">Failed BullMQ jobs accumulate unwatched</t>
   </si>
   <si>
+    <t xml:space="preserve">BullMQ `failed` fires per ATTEMPT; attempts vs exhaustion are now distinguished, counted by outcome, and only terminal failure is reported — same reasoning as OBS-A6.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-L5</t>
   </si>
   <si>
@@ -770,16 +794,25 @@
     <t xml:space="preserve">The runbook documents a log location that does not exist</t>
   </si>
   <si>
+    <t xml:space="preserve">DEPLOYMENT.md claimed logs land in ./logs. Nothing ever wrote there. Corrected to stdout + the json-file driver, with the rotation caps now set.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-M3</t>
   </si>
   <si>
     <t xml:space="preserve">Slow queries warn but are never measured</t>
   </si>
   <si>
+    <t xml:space="preserve">Every query is timed into a histogram, not just those over a hardcoded 500ms; threshold is SLOW_QUERY_MS and slow queries are counted.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-T3</t>
   </si>
   <si>
     <t xml:space="preserve">No cross-process correlation into workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">queue-producer stamps {tenant,user_id,request_id} onto every job; workers.js restores it into AsyncLocalStorage, so a failed job's log lines carry the request that enqueued it.</t>
   </si>
   <si>
     <t xml:space="preserve">OBS-I5</t>
@@ -2976,23 +3009,25 @@
       <c r="E25" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H25" s="4"/>
+      <c r="F25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>11</v>
@@ -3007,24 +3042,24 @@
         <v>14</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>27</v>
@@ -3036,19 +3071,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>27</v>
@@ -3060,19 +3095,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>27</v>
@@ -3084,19 +3119,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>27</v>
@@ -3108,19 +3143,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>27</v>
@@ -3132,19 +3167,19 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>27</v>
@@ -3156,19 +3191,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>27</v>
@@ -3180,19 +3215,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>27</v>
@@ -3204,13 +3239,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>25</v>
@@ -3228,19 +3263,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>27</v>
@@ -3252,19 +3287,19 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>27</v>
@@ -3276,19 +3311,19 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>27</v>
@@ -3300,19 +3335,19 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>27</v>
@@ -3324,19 +3359,19 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>27</v>
@@ -3348,45 +3383,45 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>27</v>
@@ -3398,13 +3433,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>25</v>
@@ -3422,13 +3457,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>25</v>
@@ -3446,19 +3481,19 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>27</v>
@@ -3470,19 +3505,19 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>27</v>
@@ -3494,19 +3529,19 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>27</v>
@@ -3518,19 +3553,19 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>27</v>
@@ -3542,19 +3577,19 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>27</v>
@@ -3566,19 +3601,19 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>27</v>
@@ -3590,19 +3625,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>27</v>
@@ -3614,19 +3649,19 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>27</v>
@@ -3638,19 +3673,19 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>27</v>
@@ -3662,19 +3697,19 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>27</v>
@@ -3686,13 +3721,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>44</v>
@@ -3710,19 +3745,19 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>27</v>
@@ -3734,19 +3769,19 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>27</v>
@@ -3758,19 +3793,19 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>27</v>
@@ -3782,19 +3817,19 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>13</v>
@@ -3803,24 +3838,24 @@
         <v>14</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>13</v>
@@ -3829,42 +3864,44 @@
         <v>14</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H61" s="4"/>
+        <v>177</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>11</v>
@@ -3879,18 +3916,18 @@
         <v>14</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>11</v>
@@ -3905,24 +3942,24 @@
         <v>14</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>13</v>
@@ -3931,24 +3968,24 @@
         <v>14</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>13</v>
@@ -3957,18 +3994,18 @@
         <v>14</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>11</v>
@@ -3986,19 +4023,19 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>13</v>
@@ -4007,18 +4044,18 @@
         <v>14</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>11</v>
@@ -4026,29 +4063,31 @@
       <c r="E68" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H68" s="4"/>
+      <c r="F68" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>27</v>
@@ -4060,19 +4099,19 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>27</v>
@@ -4084,13 +4123,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>11</v>
@@ -4105,24 +4144,24 @@
         <v>14</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>13</v>
@@ -4131,72 +4170,76 @@
         <v>14</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H73" s="4"/>
+        <v>177</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H74" s="4"/>
+        <v>222</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>13</v>
@@ -4205,24 +4248,24 @@
         <v>14</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>13</v>
@@ -4231,42 +4274,44 @@
         <v>14</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H77" s="4"/>
+        <v>222</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>25</v>
@@ -4284,19 +4329,19 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>13</v>
@@ -4305,42 +4350,44 @@
         <v>14</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H80" s="4"/>
+        <v>177</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>25</v>
@@ -4358,45 +4405,45 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>27</v>
@@ -4408,13 +4455,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>44</v>
@@ -4422,29 +4469,31 @@
       <c r="E84" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H84" s="4"/>
+      <c r="F84" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>27</v>
@@ -4456,61 +4505,65 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H86" s="4"/>
+        <v>177</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H87" s="4"/>
+        <v>177</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>44</v>
@@ -4518,29 +4571,31 @@
       <c r="E88" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H88" s="4"/>
+      <c r="F88" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>13</v>
@@ -4549,24 +4604,24 @@
         <v>14</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>13</v>
@@ -4575,24 +4630,24 @@
         <v>14</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>13</v>
@@ -4601,18 +4656,18 @@
         <v>14</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>11</v>
@@ -4630,13 +4685,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>11</v>
@@ -4651,24 +4706,24 @@
         <v>14</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>27</v>
@@ -4680,19 +4735,19 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>27</v>
@@ -4704,13 +4759,13 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>25</v>
@@ -4728,13 +4783,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>25</v>
@@ -4752,19 +4807,19 @@
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>13</v>
@@ -4773,24 +4828,24 @@
         <v>14</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>27</v>
@@ -4802,19 +4857,19 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>27</v>
@@ -4826,45 +4881,45 @@
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G101" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>27</v>
@@ -4876,13 +4931,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>44</v>
@@ -4900,13 +4955,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>44</v>
@@ -4924,19 +4979,19 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>27</v>
@@ -4948,19 +5003,19 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>27</v>
@@ -4972,19 +5027,19 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>27</v>
@@ -4996,19 +5051,19 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="D108" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>27</v>
@@ -5020,19 +5075,19 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>27</v>
@@ -5044,19 +5099,19 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>27</v>
@@ -5068,13 +5123,13 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>44</v>
@@ -5092,19 +5147,19 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>27</v>
@@ -5116,19 +5171,19 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>27</v>
@@ -5140,19 +5195,19 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>27</v>
@@ -5164,19 +5219,19 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>27</v>
@@ -5188,19 +5243,19 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>27</v>
@@ -5212,19 +5267,19 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>27</v>
@@ -5236,19 +5291,19 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>27</v>
@@ -5260,22 +5315,22 @@
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>28</v>
@@ -5284,13 +5339,13 @@
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>11</v>
@@ -5305,18 +5360,18 @@
         <v>14</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>11</v>
@@ -5334,19 +5389,19 @@
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>13</v>
@@ -5355,24 +5410,24 @@
         <v>14</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>27</v>
@@ -5384,13 +5439,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B124" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B124" s="4" t="s">
-        <v>329</v>
-      </c>
       <c r="C124" s="4" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="D124" s="8" t="s">
         <v>25</v>
@@ -5408,19 +5463,19 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>27</v>
@@ -5432,19 +5487,19 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="D126" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>27</v>
@@ -5456,19 +5511,19 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="D127" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>27</v>
@@ -5480,19 +5535,19 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>27</v>
@@ -5504,19 +5559,19 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D129" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>27</v>
@@ -5528,13 +5583,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="D130" s="8" t="s">
         <v>25</v>
@@ -5552,13 +5607,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="D131" s="8" t="s">
         <v>25</v>
@@ -5576,13 +5631,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>44</v>
@@ -5600,19 +5655,19 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>27</v>
@@ -5624,19 +5679,19 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>27</v>
@@ -5648,19 +5703,19 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="D135" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>27</v>
@@ -5672,19 +5727,19 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D136" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>27</v>
@@ -5696,19 +5751,19 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="D137" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>27</v>
@@ -5720,19 +5775,19 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>27</v>
@@ -5744,13 +5799,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="D139" s="10" t="s">
         <v>69</v>
@@ -5768,19 +5823,19 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>27</v>
@@ -5792,19 +5847,19 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>27</v>
@@ -5816,19 +5871,19 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>27</v>
@@ -5840,19 +5895,19 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>27</v>
@@ -5864,19 +5919,19 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>13</v>
@@ -5885,24 +5940,24 @@
         <v>14</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>13</v>
@@ -5911,24 +5966,24 @@
         <v>14</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>27</v>
@@ -5940,19 +5995,19 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="D147" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>27</v>
@@ -5964,19 +6019,19 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="D148" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>27</v>
@@ -5988,19 +6043,19 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="D149" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>27</v>
@@ -6012,19 +6067,19 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>27</v>
@@ -6036,19 +6091,19 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="D151" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>27</v>
@@ -6060,19 +6115,19 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="D152" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>27</v>
@@ -6084,19 +6139,19 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>27</v>
@@ -6108,19 +6163,19 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>27</v>
@@ -6132,19 +6187,19 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>27</v>
@@ -6156,19 +6211,19 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>27</v>
@@ -6180,19 +6235,19 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>27</v>
@@ -6204,19 +6259,19 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="D158" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>27</v>
@@ -6228,19 +6283,19 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="D159" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>27</v>
@@ -6252,19 +6307,19 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="D160" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>13</v>
@@ -6273,24 +6328,24 @@
         <v>14</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="D161" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>27</v>
@@ -6302,19 +6357,19 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="D162" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>27</v>
@@ -6326,19 +6381,19 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D163" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>27</v>
@@ -6350,19 +6405,19 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>13</v>
@@ -6371,24 +6426,24 @@
         <v>14</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="D165" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>27</v>
@@ -6400,45 +6455,45 @@
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="D166" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="D167" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>27</v>
@@ -6450,19 +6505,19 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="D168" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>27</v>
@@ -6474,19 +6529,19 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="D169" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>27</v>
@@ -6498,19 +6553,19 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="D170" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>27</v>
@@ -6522,19 +6577,19 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="D171" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>13</v>
@@ -6543,24 +6598,24 @@
         <v>14</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>27</v>
@@ -6572,19 +6627,19 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="D173" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>27</v>
@@ -6596,19 +6651,19 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="D174" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>27</v>
@@ -6620,19 +6675,19 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="D175" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>27</v>
@@ -6644,19 +6699,19 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>27</v>
@@ -6668,19 +6723,19 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="D177" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>13</v>
@@ -6689,24 +6744,24 @@
         <v>14</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="D178" s="13" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>27</v>
@@ -6718,19 +6773,19 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="D179" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>27</v>
@@ -6742,19 +6797,19 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>27</v>
@@ -6766,19 +6821,19 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>27</v>
@@ -6790,19 +6845,19 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>27</v>
@@ -6814,19 +6869,19 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="D183" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>27</v>
@@ -6838,19 +6893,19 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="D184" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F184" s="4" t="s">
         <v>27</v>
@@ -6862,22 +6917,22 @@
     </row>
     <row r="185" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="D185" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>28</v>
@@ -6886,22 +6941,22 @@
     </row>
     <row r="186" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="D186" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>28</v>
@@ -6910,13 +6965,13 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>11</v>
@@ -6934,13 +6989,13 @@
     </row>
     <row r="188" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>11</v>
@@ -6955,50 +7010,50 @@
         <v>14</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F189" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G189" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="F190" s="4" t="s">
         <v>27</v>
@@ -7010,13 +7065,13 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>11</v>
@@ -7034,45 +7089,45 @@
     </row>
     <row r="192" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="D192" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="D193" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F193" s="4" t="s">
         <v>27</v>
@@ -7084,13 +7139,13 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="D194" s="8" t="s">
         <v>25</v>
@@ -7108,19 +7163,19 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>27</v>
@@ -7132,19 +7187,19 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="D196" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F196" s="4" t="s">
         <v>27</v>
@@ -7156,19 +7211,19 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>27</v>
@@ -7180,13 +7235,13 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>25</v>
@@ -7204,13 +7259,13 @@
     </row>
     <row r="199" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="D199" s="9" t="s">
         <v>44</v>
@@ -7219,30 +7274,30 @@
         <v>26</v>
       </c>
       <c r="F199" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G199" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="D200" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>27</v>
@@ -7254,19 +7309,19 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="D201" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>27</v>
@@ -7278,19 +7333,19 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D202" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>27</v>
@@ -7302,13 +7357,13 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="D203" s="9" t="s">
         <v>44</v>
@@ -7326,19 +7381,19 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="D204" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>27</v>
@@ -7350,19 +7405,19 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="D205" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>27</v>
@@ -7374,19 +7429,19 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="D206" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>27</v>
@@ -7398,19 +7453,19 @@
     </row>
     <row r="207" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>13</v>
@@ -7419,24 +7474,24 @@
         <v>14</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>13</v>
@@ -7445,18 +7500,18 @@
         <v>14</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="D209" s="5" t="s">
         <v>11</v>
@@ -7471,18 +7526,18 @@
         <v>14</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="D210" s="8" t="s">
         <v>25</v>
@@ -7497,24 +7552,24 @@
         <v>14</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>27</v>
@@ -7523,18 +7578,18 @@
         <v>14</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="D212" s="10" t="s">
         <v>69</v>
@@ -7549,7 +7604,7 @@
         <v>14</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -7585,7 +7640,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -7597,7 +7652,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -7628,19 +7683,19 @@
         <v>25</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>44</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7678,7 +7733,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A6,Register!$D$2:$D$206,B$4)</f>
@@ -7711,7 +7766,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A7,Register!$D$2:$D$206,B$4)</f>
@@ -7744,7 +7799,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,B$4)</f>
@@ -7777,7 +7832,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,B$4)</f>
@@ -7810,7 +7865,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,B$4)</f>
@@ -7843,7 +7898,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,B$4)</f>
@@ -7876,7 +7931,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -7919,7 +7974,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -7935,7 +7990,7 @@
       </c>
       <c r="B15" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A15)</f>
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -7946,7 +8001,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A16)</f>
@@ -7965,7 +8020,7 @@
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,"Fixed")</f>
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -7976,7 +8031,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A18)</f>
@@ -7991,7 +8046,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A19)</f>
@@ -8006,11 +8061,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">COUNTIF(Register!$G$2:$G$206,"Verified in code")</f>
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>

--- a/doc/AUDIT_REGISTER_2026-08-04.xlsx
+++ b/doc/AUDIT_REGISTER_2026-08-04.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="578">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -323,12 +323,18 @@
     <t xml:space="preserve">Migration + data probe</t>
   </si>
   <si>
+    <t xml:space="preserve">Migration 0497: 71 CHECK constraints (66 non-negative, 5 strictly-positive rates) + asset.useful_life_months &gt; 0. All NOT VALID, so enforced on new writes immediately without failing on historical rows. CURATED not generated — stock_movement.qty is a SIGNED delta and is deliberately excluded, as are kpi_target.target_value and appraisal.actual_value. scripts/db/probe-money-constraints.js finds existing violations before VALIDATE.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-1.2</t>
   </si>
   <si>
     <t xml:space="preserve">No cross-row sum invariants (over-allocation, over-justification)</t>
   </si>
   <si>
+    <t xml:space="preserve">0497: advance.applied_amount &lt;= amount, regie_advance.justified+returned &lt;= amount. NOT VALID for the same reason.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-2.1</t>
   </si>
   <si>
@@ -338,6 +344,9 @@
     <t xml:space="preserve">Migration, careful</t>
   </si>
   <si>
+    <t xml:space="preserve">Migration 0498: nine ON DELETE CASCADE FKs on financial and inventory history changed to RESTRICT (depreciation_schedule, payment_allocation, invoice_line, supplier_invoice_line, cash_request_payment, debt_repayment, stock_movement, close_checklist, payroll_run_item). Follows the ledger's own correct pattern: block the parent delete rather than silently destroy the child.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-1.3</t>
   </si>
   <si>
@@ -356,6 +365,9 @@
     <t xml:space="preserve">Migration + dedupe</t>
   </si>
   <si>
+    <t xml:space="preserve">0498: partial UNIQUE indexes on doc_number across all 9 document tables (WHERE NOT NULL, so drafts do not collide). No NOT VALID exists for uniqueness, so scripts/db/probe-doc-numbers.js must run first — it lists collisions before they become a failed deploy.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-1.8</t>
   </si>
   <si>
@@ -467,6 +479,9 @@
     <t xml:space="preserve">Missing uniqueness on document numbers and payment allocations</t>
   </si>
   <si>
+    <t xml:space="preserve">0497: UNIQUE (receipt_id, invoice_id) on payment_allocation — the same receipt could be allocated to one invoice twice. Plus the doc_number indexes in 0498.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-1.4</t>
   </si>
   <si>
@@ -479,6 +494,9 @@
     <t xml:space="preserve">chart_of_accounts and other self-referencing hierarchies have no cycle guard</t>
   </si>
   <si>
+    <t xml:space="preserve">0497: chart_of_accounts cannot be its own parent — a row made its own parent spun every recursive walk.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-2.3</t>
   </si>
   <si>
@@ -515,6 +533,9 @@
     <t xml:space="preserve">Remove or implement</t>
   </si>
   <si>
+    <t xml:space="preserve">The RLS apparatus is gone: RLS_READ_ENFORCE, queryWithContext, and the superuser warning. Confirmed zero CREATE POLICY / ROW LEVEL SECURITY anywhere in migrations/ — it set a GUC for policies that do not exist, costing a round-trip per read and filtering nothing while reading as though isolation were on.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-4.2</t>
   </si>
   <si>
@@ -522,6 +543,9 @@
   </si>
   <si>
     <t xml:space="preserve">Remove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">services/numbering.service.js and services/notifications.service.js deleted (verified zero importers each). push.service.js's `shared.push_subscription` fallback removed — the schema has never existed, so the branch could only ever return 'no table', and its sole caller was one of the deleted files.</t>
   </si>
   <si>
     <t xml:space="preserve">DI-5.6</t>
@@ -3109,23 +3133,25 @@
       <c r="E29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H29" s="4"/>
+      <c r="F29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>11</v>
@@ -3133,53 +3159,57 @@
       <c r="E30" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="4"/>
+      <c r="F30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H31" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>27</v>
@@ -3191,43 +3221,45 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H33" s="4"/>
+        <v>112</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>27</v>
@@ -3239,13 +3271,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>25</v>
@@ -3263,19 +3295,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>27</v>
@@ -3287,19 +3319,19 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>27</v>
@@ -3311,19 +3343,19 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>27</v>
@@ -3335,19 +3367,19 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>27</v>
@@ -3359,19 +3391,19 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>27</v>
@@ -3383,39 +3415,39 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>25</v>
@@ -3433,13 +3465,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>25</v>
@@ -3457,13 +3489,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>25</v>
@@ -3481,19 +3513,19 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>27</v>
@@ -3505,19 +3537,19 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>27</v>
@@ -3529,43 +3561,45 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H47" s="4"/>
+        <v>112</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>27</v>
@@ -3577,43 +3611,45 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H49" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>27</v>
@@ -3625,19 +3661,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>27</v>
@@ -3649,19 +3685,19 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>27</v>
@@ -3673,61 +3709,65 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H53" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H54" s="4"/>
+        <v>172</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>44</v>
@@ -3745,19 +3785,19 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>27</v>
@@ -3769,19 +3809,19 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>27</v>
@@ -3793,19 +3833,19 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>27</v>
@@ -3817,19 +3857,19 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>13</v>
@@ -3838,24 +3878,24 @@
         <v>14</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>13</v>
@@ -3864,24 +3904,24 @@
         <v>14</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>13</v>
@@ -3890,18 +3930,18 @@
         <v>14</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>11</v>
@@ -3916,18 +3956,18 @@
         <v>14</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>11</v>
@@ -3942,24 +3982,24 @@
         <v>14</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>13</v>
@@ -3968,24 +4008,24 @@
         <v>14</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>13</v>
@@ -3994,18 +4034,18 @@
         <v>14</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>11</v>
@@ -4023,19 +4063,19 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>13</v>
@@ -4044,18 +4084,18 @@
         <v>14</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>11</v>
@@ -4070,24 +4110,24 @@
         <v>14</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>27</v>
@@ -4099,19 +4139,19 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>27</v>
@@ -4123,13 +4163,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>11</v>
@@ -4144,24 +4184,24 @@
         <v>14</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>13</v>
@@ -4170,24 +4210,24 @@
         <v>14</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>13</v>
@@ -4196,24 +4236,24 @@
         <v>14</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>13</v>
@@ -4222,24 +4262,24 @@
         <v>14</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>13</v>
@@ -4248,24 +4288,24 @@
         <v>14</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>13</v>
@@ -4274,24 +4314,24 @@
         <v>14</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>13</v>
@@ -4300,18 +4340,18 @@
         <v>14</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>25</v>
@@ -4329,19 +4369,19 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>13</v>
@@ -4350,24 +4390,24 @@
         <v>14</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>13</v>
@@ -4376,18 +4416,18 @@
         <v>14</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>25</v>
@@ -4405,45 +4445,45 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>27</v>
@@ -4455,13 +4495,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>44</v>
@@ -4476,24 +4516,24 @@
         <v>14</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>27</v>
@@ -4505,19 +4545,19 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>13</v>
@@ -4526,24 +4566,24 @@
         <v>14</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>13</v>
@@ -4552,18 +4592,18 @@
         <v>14</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>44</v>
@@ -4578,24 +4618,24 @@
         <v>14</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>13</v>
@@ -4604,24 +4644,24 @@
         <v>14</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>13</v>
@@ -4630,24 +4670,24 @@
         <v>14</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>13</v>
@@ -4656,18 +4696,18 @@
         <v>14</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>11</v>
@@ -4685,13 +4725,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>11</v>
@@ -4706,24 +4746,24 @@
         <v>14</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>27</v>
@@ -4735,19 +4775,19 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>27</v>
@@ -4759,13 +4799,13 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>25</v>
@@ -4783,13 +4823,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>25</v>
@@ -4807,19 +4847,19 @@
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>13</v>
@@ -4828,24 +4868,24 @@
         <v>14</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>27</v>
@@ -4857,19 +4897,19 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>27</v>
@@ -4881,45 +4921,45 @@
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G101" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>27</v>
@@ -4931,13 +4971,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>44</v>
@@ -4955,13 +4995,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>44</v>
@@ -4979,19 +5019,19 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>27</v>
@@ -5003,19 +5043,19 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>27</v>
@@ -5027,19 +5067,19 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>27</v>
@@ -5051,19 +5091,19 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D108" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>27</v>
@@ -5075,19 +5115,19 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>27</v>
@@ -5099,19 +5139,19 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>27</v>
@@ -5123,13 +5163,13 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>44</v>
@@ -5147,19 +5187,19 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>27</v>
@@ -5171,19 +5211,19 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>27</v>
@@ -5195,19 +5235,19 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>27</v>
@@ -5219,19 +5259,19 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>27</v>
@@ -5243,19 +5283,19 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>27</v>
@@ -5267,19 +5307,19 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>27</v>
@@ -5291,19 +5331,19 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>27</v>
@@ -5315,22 +5355,22 @@
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>28</v>
@@ -5339,13 +5379,13 @@
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>11</v>
@@ -5360,18 +5400,18 @@
         <v>14</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>11</v>
@@ -5389,19 +5429,19 @@
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>13</v>
@@ -5410,24 +5450,24 @@
         <v>14</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B123" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="B123" s="4" t="s">
-        <v>340</v>
-      </c>
       <c r="C123" s="4" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>27</v>
@@ -5439,13 +5479,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D124" s="8" t="s">
         <v>25</v>
@@ -5463,19 +5503,19 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>27</v>
@@ -5487,19 +5527,19 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D126" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>27</v>
@@ -5511,19 +5551,19 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D127" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>27</v>
@@ -5535,19 +5575,19 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>27</v>
@@ -5559,19 +5599,19 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="D129" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>27</v>
@@ -5583,13 +5623,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D130" s="8" t="s">
         <v>25</v>
@@ -5607,13 +5647,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D131" s="8" t="s">
         <v>25</v>
@@ -5631,13 +5671,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>44</v>
@@ -5655,19 +5695,19 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>27</v>
@@ -5679,19 +5719,19 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>27</v>
@@ -5703,19 +5743,19 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D135" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>27</v>
@@ -5727,19 +5767,19 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="D136" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>27</v>
@@ -5751,19 +5791,19 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="D137" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>27</v>
@@ -5775,19 +5815,19 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>27</v>
@@ -5799,13 +5839,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="D139" s="10" t="s">
         <v>69</v>
@@ -5823,19 +5863,19 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>27</v>
@@ -5847,19 +5887,19 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>27</v>
@@ -5871,19 +5911,19 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>27</v>
@@ -5895,19 +5935,19 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>27</v>
@@ -5919,19 +5959,19 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>13</v>
@@ -5940,24 +5980,24 @@
         <v>14</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>13</v>
@@ -5966,24 +6006,24 @@
         <v>14</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>27</v>
@@ -5995,19 +6035,19 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D147" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>27</v>
@@ -6019,19 +6059,19 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D148" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>27</v>
@@ -6043,19 +6083,19 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D149" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>27</v>
@@ -6067,19 +6107,19 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>27</v>
@@ -6091,19 +6131,19 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="D151" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>27</v>
@@ -6115,19 +6155,19 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="D152" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>27</v>
@@ -6139,19 +6179,19 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>27</v>
@@ -6163,19 +6203,19 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>27</v>
@@ -6187,19 +6227,19 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>27</v>
@@ -6211,19 +6251,19 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>27</v>
@@ -6235,19 +6275,19 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>27</v>
@@ -6259,19 +6299,19 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D158" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>27</v>
@@ -6283,19 +6323,19 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="D159" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>27</v>
@@ -6307,19 +6347,19 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="D160" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>13</v>
@@ -6328,24 +6368,24 @@
         <v>14</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="D161" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>27</v>
@@ -6357,19 +6397,19 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="D162" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>27</v>
@@ -6381,19 +6421,19 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="D163" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>27</v>
@@ -6405,19 +6445,19 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>13</v>
@@ -6426,24 +6466,24 @@
         <v>14</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D165" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>27</v>
@@ -6455,45 +6495,45 @@
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D166" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="D167" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>27</v>
@@ -6505,19 +6545,19 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="D168" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>27</v>
@@ -6529,19 +6569,19 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D169" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>27</v>
@@ -6553,19 +6593,19 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="D170" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>27</v>
@@ -6577,19 +6617,19 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D171" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>13</v>
@@ -6598,24 +6638,24 @@
         <v>14</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>27</v>
@@ -6627,19 +6667,19 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="D173" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>27</v>
@@ -6651,19 +6691,19 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D174" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>27</v>
@@ -6675,19 +6715,19 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="D175" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>27</v>
@@ -6699,19 +6739,19 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>27</v>
@@ -6723,19 +6763,19 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="D177" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>13</v>
@@ -6744,24 +6784,24 @@
         <v>14</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D178" s="13" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>27</v>
@@ -6773,19 +6813,19 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D179" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>27</v>
@@ -6797,19 +6837,19 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>27</v>
@@ -6821,19 +6861,19 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>27</v>
@@ -6845,19 +6885,19 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>27</v>
@@ -6869,19 +6909,19 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="D183" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>27</v>
@@ -6893,19 +6933,19 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="D184" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F184" s="4" t="s">
         <v>27</v>
@@ -6917,22 +6957,22 @@
     </row>
     <row r="185" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="D185" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>28</v>
@@ -6941,22 +6981,22 @@
     </row>
     <row r="186" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D186" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>28</v>
@@ -6965,13 +7005,13 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>11</v>
@@ -6989,13 +7029,13 @@
     </row>
     <row r="188" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>11</v>
@@ -7010,50 +7050,50 @@
         <v>14</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F189" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G189" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F190" s="4" t="s">
         <v>27</v>
@@ -7065,13 +7105,13 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>11</v>
@@ -7089,45 +7129,45 @@
     </row>
     <row r="192" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="D192" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D193" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F193" s="4" t="s">
         <v>27</v>
@@ -7139,13 +7179,13 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="D194" s="8" t="s">
         <v>25</v>
@@ -7163,19 +7203,19 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>27</v>
@@ -7187,19 +7227,19 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D196" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F196" s="4" t="s">
         <v>27</v>
@@ -7211,19 +7251,19 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>27</v>
@@ -7235,13 +7275,13 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>25</v>
@@ -7259,13 +7299,13 @@
     </row>
     <row r="199" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="D199" s="9" t="s">
         <v>44</v>
@@ -7274,30 +7314,30 @@
         <v>26</v>
       </c>
       <c r="F199" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G199" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D200" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>27</v>
@@ -7309,19 +7349,19 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="D201" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>27</v>
@@ -7333,19 +7373,19 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="D202" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>27</v>
@@ -7357,13 +7397,13 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D203" s="9" t="s">
         <v>44</v>
@@ -7381,19 +7421,19 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D204" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>27</v>
@@ -7405,19 +7445,19 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="D205" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>27</v>
@@ -7429,19 +7469,19 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D206" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>27</v>
@@ -7453,19 +7493,19 @@
     </row>
     <row r="207" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>13</v>
@@ -7474,24 +7514,24 @@
         <v>14</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>13</v>
@@ -7500,18 +7540,18 @@
         <v>14</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D209" s="5" t="s">
         <v>11</v>
@@ -7526,18 +7566,18 @@
         <v>14</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D210" s="8" t="s">
         <v>25</v>
@@ -7552,24 +7592,24 @@
         <v>14</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>27</v>
@@ -7578,18 +7618,18 @@
         <v>14</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="D212" s="10" t="s">
         <v>69</v>
@@ -7604,7 +7644,7 @@
         <v>14</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -7640,7 +7680,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -7652,7 +7692,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -7683,19 +7723,19 @@
         <v>25</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>44</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7766,7 +7806,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A7,Register!$D$2:$D$206,B$4)</f>
@@ -7799,7 +7839,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,B$4)</f>
@@ -7832,7 +7872,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,B$4)</f>
@@ -7865,7 +7905,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,B$4)</f>
@@ -7898,7 +7938,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,B$4)</f>
@@ -7931,7 +7971,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -7974,7 +8014,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -7990,7 +8030,7 @@
       </c>
       <c r="B15" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A15)</f>
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -8001,7 +8041,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A16)</f>
@@ -8020,7 +8060,7 @@
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,"Fixed")</f>
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -8031,7 +8071,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A18)</f>
@@ -8046,7 +8086,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A19)</f>
@@ -8061,11 +8101,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">COUNTIF(Register!$G$2:$G$206,"Verified in code")</f>
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>

--- a/doc/AUDIT_REGISTER_2026-08-04.xlsx
+++ b/doc/AUDIT_REGISTER_2026-08-04.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="582">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -305,6 +305,9 @@
     <t xml:space="preserve">Code + constraint</t>
   </si>
   <si>
+    <t xml:space="preserve">inventory move() is now ONE transaction, reads the head FOR UPDATE, and applies a SIGNED delta in SQL with `WHERE qty_on_hand + $2 &gt;= 0` — so the floor is enforced by the database against the row it holds, not by a JS check that ran before the lock. Closes lost-update, the racy guard, and balance/journal divergence. 0497 adds CHECK (qty_on_hand &gt;= 0) as the last line.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-5.2</t>
   </si>
   <si>
@@ -314,6 +317,9 @@
     <t xml:space="preserve">Code, mechanical</t>
   </si>
   <si>
+    <t xml:space="preserve">shared/db/tx.js atomically(); create/update/archive in the CRUD kit are each one unit. 25 modules build on makeService, so one helper covers all of them. The archive ordering comment is kept but is no longer load-bearing — a failure now rolls back instead of stranding a soft_delete row asserting a deletion that never happened.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-1.1</t>
   </si>
   <si>
@@ -443,10 +449,16 @@
     <t xml:space="preserve">Receipt allocation reads unlocked and can over-allocate</t>
   </si>
   <si>
+    <t xml:space="preserve">repo.openInvoices({forUpdate}) locks the invoice rows in the same order the FIFO allocation walks them (oldest first — also a consistent lock order, so two concurrent receipts cannot deadlock). Only post(), which writes allocations, locks; the read-only callers do not. Over-allocation made outstanding negative, which then HID the invoice from ageing and dunning because the query filters outstanding &gt; 0.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI-5.4</t>
   </si>
   <si>
     <t xml:space="preserve">Tax-code supersession splits across two transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supersedeCode wraps expire + addCode in one transaction via atomically(); addCode joins rather than opening its own. Previously the expiry COMMITTED before the replacement was attempted, so a bad rate left NO row effective from that date — and every invoice from that date forward failed to post until someone inserted it by hand.</t>
   </si>
   <si>
     <t xml:space="preserve">DI-6.2</t>
@@ -3085,53 +3097,57 @@
       <c r="E27" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="4"/>
+      <c r="F27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H28" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>13</v>
@@ -3140,24 +3156,24 @@
         <v>14</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>13</v>
@@ -3166,24 +3182,24 @@
         <v>14</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>13</v>
@@ -3192,24 +3208,24 @@
         <v>14</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>27</v>
@@ -3221,19 +3237,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>13</v>
@@ -3242,24 +3258,24 @@
         <v>14</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>27</v>
@@ -3271,13 +3287,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>25</v>
@@ -3295,19 +3311,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>27</v>
@@ -3319,19 +3335,19 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>27</v>
@@ -3343,19 +3359,19 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>27</v>
@@ -3367,19 +3383,19 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>27</v>
@@ -3391,19 +3407,19 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>27</v>
@@ -3415,39 +3431,39 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>25</v>
@@ -3455,23 +3471,25 @@
       <c r="E42" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H42" s="4"/>
+      <c r="F42" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>25</v>
@@ -3479,23 +3497,25 @@
       <c r="E43" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H43" s="4"/>
+      <c r="F43" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>25</v>
@@ -3513,19 +3533,19 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>27</v>
@@ -3537,19 +3557,19 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>27</v>
@@ -3561,19 +3581,19 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>13</v>
@@ -3582,24 +3602,24 @@
         <v>14</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>27</v>
@@ -3611,19 +3631,19 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>13</v>
@@ -3632,24 +3652,24 @@
         <v>14</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>27</v>
@@ -3661,19 +3681,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>27</v>
@@ -3685,19 +3705,19 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>27</v>
@@ -3709,19 +3729,19 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>13</v>
@@ -3730,24 +3750,24 @@
         <v>14</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>13</v>
@@ -3756,18 +3776,18 @@
         <v>14</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>44</v>
@@ -3785,19 +3805,19 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>27</v>
@@ -3809,19 +3829,19 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>27</v>
@@ -3833,19 +3853,19 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>27</v>
@@ -3857,19 +3877,19 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>13</v>
@@ -3878,24 +3898,24 @@
         <v>14</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>183</v>
-      </c>
       <c r="C60" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>13</v>
@@ -3904,24 +3924,24 @@
         <v>14</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>13</v>
@@ -3930,18 +3950,18 @@
         <v>14</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>11</v>
@@ -3956,18 +3976,18 @@
         <v>14</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>11</v>
@@ -3982,24 +4002,24 @@
         <v>14</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>13</v>
@@ -4008,24 +4028,24 @@
         <v>14</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>13</v>
@@ -4034,18 +4054,18 @@
         <v>14</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>11</v>
@@ -4063,19 +4083,19 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>13</v>
@@ -4084,18 +4104,18 @@
         <v>14</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>11</v>
@@ -4110,24 +4130,24 @@
         <v>14</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>27</v>
@@ -4139,19 +4159,19 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>27</v>
@@ -4163,13 +4183,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>11</v>
@@ -4184,24 +4204,24 @@
         <v>14</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>13</v>
@@ -4210,24 +4230,24 @@
         <v>14</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>13</v>
@@ -4236,24 +4256,24 @@
         <v>14</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>13</v>
@@ -4262,24 +4282,24 @@
         <v>14</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>13</v>
@@ -4288,24 +4308,24 @@
         <v>14</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>13</v>
@@ -4314,24 +4334,24 @@
         <v>14</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>13</v>
@@ -4340,18 +4360,18 @@
         <v>14</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>25</v>
@@ -4369,19 +4389,19 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>13</v>
@@ -4390,24 +4410,24 @@
         <v>14</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>13</v>
@@ -4416,18 +4436,18 @@
         <v>14</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>25</v>
@@ -4445,45 +4465,45 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>27</v>
@@ -4495,13 +4515,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>44</v>
@@ -4516,24 +4536,24 @@
         <v>14</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>27</v>
@@ -4545,19 +4565,19 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>13</v>
@@ -4566,24 +4586,24 @@
         <v>14</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>13</v>
@@ -4592,18 +4612,18 @@
         <v>14</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>44</v>
@@ -4618,24 +4638,24 @@
         <v>14</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>13</v>
@@ -4644,24 +4664,24 @@
         <v>14</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>13</v>
@@ -4670,24 +4690,24 @@
         <v>14</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>275</v>
-      </c>
       <c r="C91" s="4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>13</v>
@@ -4696,18 +4716,18 @@
         <v>14</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>11</v>
@@ -4725,13 +4745,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>11</v>
@@ -4746,24 +4766,24 @@
         <v>14</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>27</v>
@@ -4775,19 +4795,19 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>27</v>
@@ -4799,13 +4819,13 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>25</v>
@@ -4823,13 +4843,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>25</v>
@@ -4847,19 +4867,19 @@
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>13</v>
@@ -4868,24 +4888,24 @@
         <v>14</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>27</v>
@@ -4897,19 +4917,19 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>27</v>
@@ -4921,45 +4941,45 @@
     </row>
     <row r="101" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G101" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>27</v>
@@ -4971,13 +4991,13 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>44</v>
@@ -4995,13 +5015,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>44</v>
@@ -5019,19 +5039,19 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>27</v>
@@ -5043,19 +5063,19 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>27</v>
@@ -5067,19 +5087,19 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>27</v>
@@ -5091,19 +5111,19 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D108" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>27</v>
@@ -5115,19 +5135,19 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>27</v>
@@ -5139,19 +5159,19 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>27</v>
@@ -5163,13 +5183,13 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>44</v>
@@ -5187,19 +5207,19 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>27</v>
@@ -5211,19 +5231,19 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>27</v>
@@ -5235,19 +5255,19 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>27</v>
@@ -5259,19 +5279,19 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>27</v>
@@ -5283,19 +5303,19 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>27</v>
@@ -5307,19 +5327,19 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>27</v>
@@ -5331,19 +5351,19 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D118" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>27</v>
@@ -5355,22 +5375,22 @@
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G119" s="4" t="s">
         <v>28</v>
@@ -5379,13 +5399,13 @@
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>11</v>
@@ -5400,18 +5420,18 @@
         <v>14</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>11</v>
@@ -5429,19 +5449,19 @@
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>13</v>
@@ -5450,24 +5470,24 @@
         <v>14</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>27</v>
@@ -5479,13 +5499,13 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D124" s="8" t="s">
         <v>25</v>
@@ -5503,19 +5523,19 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>27</v>
@@ -5527,19 +5547,19 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D126" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>27</v>
@@ -5551,19 +5571,19 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D127" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>27</v>
@@ -5575,19 +5595,19 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>27</v>
@@ -5599,19 +5619,19 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D129" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>27</v>
@@ -5623,13 +5643,13 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D130" s="8" t="s">
         <v>25</v>
@@ -5647,13 +5667,13 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D131" s="8" t="s">
         <v>25</v>
@@ -5671,13 +5691,13 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>44</v>
@@ -5695,19 +5715,19 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>27</v>
@@ -5719,19 +5739,19 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>27</v>
@@ -5743,19 +5763,19 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D135" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>27</v>
@@ -5767,19 +5787,19 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D136" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>27</v>
@@ -5791,19 +5811,19 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D137" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>27</v>
@@ -5815,19 +5835,19 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>27</v>
@@ -5839,13 +5859,13 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D139" s="10" t="s">
         <v>69</v>
@@ -5863,19 +5883,19 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>27</v>
@@ -5887,19 +5907,19 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>27</v>
@@ -5911,19 +5931,19 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>27</v>
@@ -5935,19 +5955,19 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>27</v>
@@ -5959,19 +5979,19 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>13</v>
@@ -5980,24 +6000,24 @@
         <v>14</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>13</v>
@@ -6006,24 +6026,24 @@
         <v>14</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>27</v>
@@ -6035,19 +6055,19 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D147" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>27</v>
@@ -6059,19 +6079,19 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D148" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>27</v>
@@ -6083,19 +6103,19 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D149" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>27</v>
@@ -6107,19 +6127,19 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D150" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>27</v>
@@ -6131,19 +6151,19 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D151" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>27</v>
@@ -6155,19 +6175,19 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D152" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>27</v>
@@ -6179,19 +6199,19 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>27</v>
@@ -6203,19 +6223,19 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>27</v>
@@ -6227,19 +6247,19 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>27</v>
@@ -6251,19 +6271,19 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>27</v>
@@ -6275,19 +6295,19 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>27</v>
@@ -6299,19 +6319,19 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D158" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>27</v>
@@ -6323,19 +6343,19 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D159" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>27</v>
@@ -6347,19 +6367,19 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D160" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>13</v>
@@ -6368,24 +6388,24 @@
         <v>14</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D161" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>27</v>
@@ -6397,19 +6417,19 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D162" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>27</v>
@@ -6421,19 +6441,19 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D163" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>27</v>
@@ -6445,19 +6465,19 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>13</v>
@@ -6466,24 +6486,24 @@
         <v>14</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D165" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>27</v>
@@ -6495,45 +6515,45 @@
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D166" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G166" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D167" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>27</v>
@@ -6545,19 +6565,19 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D168" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>27</v>
@@ -6569,19 +6589,19 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D169" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>27</v>
@@ -6593,19 +6613,19 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D170" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>27</v>
@@ -6617,19 +6637,19 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D171" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>13</v>
@@ -6638,24 +6658,24 @@
         <v>14</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>27</v>
@@ -6667,19 +6687,19 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D173" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>27</v>
@@ -6691,19 +6711,19 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D174" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>27</v>
@@ -6715,19 +6735,19 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D175" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>27</v>
@@ -6739,19 +6759,19 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>27</v>
@@ -6763,19 +6783,19 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D177" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>13</v>
@@ -6784,24 +6804,24 @@
         <v>14</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D178" s="13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>27</v>
@@ -6813,19 +6833,19 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D179" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>27</v>
@@ -6837,19 +6857,19 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>27</v>
@@ -6861,19 +6881,19 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>27</v>
@@ -6885,19 +6905,19 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="D182" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="B182" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="D182" s="14" t="s">
-        <v>488</v>
-      </c>
       <c r="E182" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>27</v>
@@ -6909,19 +6929,19 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D183" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>27</v>
@@ -6933,19 +6953,19 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D184" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F184" s="4" t="s">
         <v>27</v>
@@ -6957,22 +6977,22 @@
     </row>
     <row r="185" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D185" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F185" s="12" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>28</v>
@@ -6981,22 +7001,22 @@
     </row>
     <row r="186" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D186" s="10" t="s">
         <v>69</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F186" s="12" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>28</v>
@@ -7005,13 +7025,13 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>11</v>
@@ -7029,13 +7049,13 @@
     </row>
     <row r="188" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>11</v>
@@ -7050,50 +7070,50 @@
         <v>14</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F189" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G189" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F190" s="4" t="s">
         <v>27</v>
@@ -7105,13 +7125,13 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>11</v>
@@ -7129,45 +7149,45 @@
     </row>
     <row r="192" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D192" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D193" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F193" s="4" t="s">
         <v>27</v>
@@ -7179,13 +7199,13 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D194" s="8" t="s">
         <v>25</v>
@@ -7203,19 +7223,19 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>27</v>
@@ -7227,19 +7247,19 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D196" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F196" s="4" t="s">
         <v>27</v>
@@ -7251,19 +7271,19 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>27</v>
@@ -7275,13 +7295,13 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>25</v>
@@ -7299,13 +7319,13 @@
     </row>
     <row r="199" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D199" s="9" t="s">
         <v>44</v>
@@ -7314,30 +7334,30 @@
         <v>26</v>
       </c>
       <c r="F199" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G199" s="7" t="s">
         <v>14</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D200" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>27</v>
@@ -7349,19 +7369,19 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D201" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>27</v>
@@ -7373,19 +7393,19 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D202" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>27</v>
@@ -7397,13 +7417,13 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D203" s="9" t="s">
         <v>44</v>
@@ -7421,19 +7441,19 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D204" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>27</v>
@@ -7445,19 +7465,19 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D205" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>27</v>
@@ -7469,19 +7489,19 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D206" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>27</v>
@@ -7493,19 +7513,19 @@
     </row>
     <row r="207" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>13</v>
@@ -7514,24 +7534,24 @@
         <v>14</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>13</v>
@@ -7540,18 +7560,18 @@
         <v>14</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D209" s="5" t="s">
         <v>11</v>
@@ -7566,18 +7586,18 @@
         <v>14</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B210" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D210" s="8" t="s">
         <v>25</v>
@@ -7592,24 +7612,24 @@
         <v>14</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>27</v>
@@ -7618,18 +7638,18 @@
         <v>14</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D212" s="10" t="s">
         <v>69</v>
@@ -7644,7 +7664,7 @@
         <v>14</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -7680,7 +7700,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -7692,7 +7712,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -7723,19 +7743,19 @@
         <v>25</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>44</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>69</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7806,7 +7826,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A7,Register!$D$2:$D$206,B$4)</f>
@@ -7839,7 +7859,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,B$4)</f>
@@ -7872,7 +7892,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,B$4)</f>
@@ -7905,7 +7925,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,B$4)</f>
@@ -7938,7 +7958,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,B$4)</f>
@@ -7971,7 +7991,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">SUM(B5:B11)</f>
@@ -8014,7 +8034,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -8030,7 +8050,7 @@
       </c>
       <c r="B15" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A15)</f>
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
@@ -8041,7 +8061,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A16)</f>
@@ -8060,7 +8080,7 @@
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,"Fixed")</f>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -8071,7 +8091,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A18)</f>
@@ -8086,7 +8106,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">COUNTIF(Register!$F$2:$F$206,$A19)</f>
@@ -8101,11 +8121,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">COUNTIF(Register!$G$2:$G$206,"Verified in code")</f>
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>

--- a/doc/AUDIT_REGISTER_2026-08-04.xlsx
+++ b/doc/AUDIT_REGISTER_2026-08-04.xlsx
@@ -188,7 +188,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -330,6 +330,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2202,15 +2205,19 @@
       </c>
       <c r="F37" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G37" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H37" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H37" s="48" t="inlineStr">
+        <is>
+          <t>~60 tenant columns are REFERENCES app_user(user_id); identity is pinned to the LIVE schema while business writes go to whichever schema the request selected, so a valid live user id raises 23503 beside sandbox data. emit.js guarded its own actor columns; the finding was that the guard was applied INCONSISTENTLY. All 15 raw `&lt;x&gt;_by: actor.user_id` writes across 13 services now go through resolveActorId (governance, extra_charge_simulation, margin_simulation, credit_note, final_invoice, journal_entry, appraisal, hr_query, hr_sanction, success_story, smartcomm, report, inventory.moved_by, cycle_count.counted_by). PREVENTION, because this is a class of defect that repairs itself back into existence the next time somebody adds an `_by` column: scripts/check-actor-fk-guard.js fails the build on a raw one with the reason and the remedy, wired into ci.yaml. Verified to bite (reintroducing one fails it) and green after. wms-inventory.test.js now models app_user per-schema and asserts both directions — the actor resolves when present, and a NULL is written rather than the movement failing when absent.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="25">
       <c r="A38" s="27" t="inlineStr">
@@ -2282,15 +2289,19 @@
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G39" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H39" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H39" s="28" t="inlineStr">
+        <is>
+          <t>migrateAllTenants was a bare loop with no try/catch, so the first failure aborted it and split the fleet at an arbitrary point with NOTHING RECORDING WHERE — during a deploy, while the new image expecting the new schema rolled out to all of them. It now continues past a failure, records per-tenant outcome, and throws afterwards so the deploy still goes red having done as much as it safely could. Continue rather than stop deliberately: a tenant-specific cause should not punish everyone after it in the list, and a systematic cause produces 'all 12 failed' rather than 'the first one failed'. Plus fleetSchemaStatus() + scripts/db/fleet-status.js, reading each tenant's own ledger so it reports what was APPLIED not what someone believes was; wired into CI.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="25">
       <c r="A40" s="27" t="inlineStr">
@@ -2320,15 +2331,19 @@
       </c>
       <c r="F40" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G40" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H40" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="inlineStr">
+        <is>
+          <t>Migration 0503 adds the missing created_at with ADD COLUMN IF NOT EXISTS — the right instrument because the two CREATE TABLE files disagree about history and this converges both without needing to know which ran. The column is documented as 'not before this migration' rather than pretending its backfilled now() is authoritative for historical rows. Neither original file is edited: editing an applied migration changes nothing on a database that already ran it. Plus scripts/db/check-schema-drift.js in CI. Its first version compared table names GLOBALLY and reported 4 conflicts, 3 of them false — tenant and platform are separate databases that legitimately share ai_vendor_credential, ai_document and ai_chunk. Scoped per database it reports exactly the one real conflict, and it recognises a later ALTER as the resolution so it does not stay red forever after the fix. Proven both ways: red with 0503 reverted, green with it restored.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="25">
       <c r="A41" s="27" t="inlineStr">
@@ -2736,15 +2751,19 @@
       </c>
       <c r="F50" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G50" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H50" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H50" s="48" t="inlineStr">
+        <is>
+          <t>migrations/tenant/0505, part 2. A DECISION, recorded rather than a behaviour change: ON UPDATE stays NO ACTION on the natural text keys (chart_of_accounts.code, currency.code). The audit's own reading is that this is arguably CORRECT for a statutory chart — a posted OHADA code identifies those postings forever, and ON UPDATE CASCADE would make a rename succeed silently across twelve tables, rewriting the meaning of historical entries with no audit record that the account was ever called anything else. The complaint was that it was undocumented while the COA service exposes edit paths, so a maintainer could not tell a deliberate restriction from an oversight and the next person to hit the FK violation would quite likely 'fix' it with CASCADE. Now a COMMENT ON COLUMN on both, which lives in the database, survives dump/restore, and shows up in \d+.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="25">
       <c r="A51" s="27" t="inlineStr">
@@ -2812,15 +2831,19 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G52" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H52" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H52" s="48" t="inlineStr">
+        <is>
+          <t>migrations/tenant/0506_leave_approval_repair.sql. 0467/0468 end their DO blocks with EXCEPTION WHEN OTHERS THEN NULL, so any failure was discarded and the migration recorded SUCCESS — leaving the tenant with no leave-approval workflow, which makes executor.start() return autoApproved, the calling module discard that flag, and the request sit forever without being rejected or queued (W8/W11). Not editable in place: the migrator keys the ledger on filename (DATA 3.1) and both are applied everywhere, so only a new file reaches an affected tenant — the same reasoning 0492 gives for the identical defect in 0469. Takes 0492's treatment: idempotent (no-op where 0467/0468 worked), narrow exception scope, and RAISE WARNING naming the schema, the SQLSTATE and the consequence instead of silence. Still non-fatal — a convenience seed must not block a deploy — but never again invisible. Reports how many missing approval tasks it opened.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="25">
       <c r="A53" s="27" t="inlineStr">
@@ -2934,15 +2957,19 @@
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G55" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H55" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H55" s="48" t="inlineStr">
+        <is>
+          <t>provisionTenant's five platform writes (tenant upsert, tenant_database, subdomain, status='LIVE', audit) ran on a bare client with no BEGIN, each autocommitting, so a failure part-way left a tenant registered with no database row or no subdomain, or stuck in PROVISIONING with its schema fully built and nothing routing to it — every one needing a human to unpick. Now one transaction with ROLLBACK on failure (and a failed ROLLBACK never masks the original error). The tenant DATABASE stays deliberately outside it and the code says why: CREATE DATABASE cannot participate in a transaction on another connection, and the asymmetry is the right way round — an orphaned database with no platform row is inert and re-provisioning is idempotent, whereas a platform row pointing at a database that does not exist routes live traffic into a 500. wipeSandbox likewise: DROP SCHEMA -&gt; CREATE -&gt; ledger DELETE -&gt; re-apply -&gt; mirror is now atomic, and Postgres CAN roll those back, so a crash mid-rebuild no longer leaves a tenant with NO sandbox schema and a ledger claiming the scopes were applied (which made self-healing impossible). Verified by the tenant-provisioning tests, including the tripwire this batch deliberately left behind: the test that asserted the OLD non-transactional behaviour failed on the fix and was rewritten to assert the new one, plus rollback and no-re-projection cases.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="25">
       <c r="A56" s="27" t="inlineStr">
@@ -3014,15 +3041,19 @@
       </c>
       <c r="F57" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G57" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H57" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H57" s="48" t="inlineStr">
+        <is>
+          <t>migrations/tenant/0504, part 1. Seven composite indexes on columns that gate correctness-critical queries: invoice(status,type), payment_allocation(invoice_id), journal_line(account_code,entry_id), journal_entry(entity_id,period_id,status), stock_movement(inventory_item_id,moved_at DESC), depreciation_schedule(asset_id,posted), and accounting_period(entity_id,starts_on,ends_on) — that last backs getPeriodForDate, which runs on EVERY journal post and had no supporting index at all. Plain CREATE INDEX IF NOT EXISTS, not CONCURRENTLY, for the reason 0496/0500 already document (the migrator sends each file as one multi-statement simple query, which Postgres wraps in an implicit transaction where CONCURRENTLY cannot run). Rollback stated in the header. VERIFIED BY PARSING ONLY — see the note on 0505.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="25">
       <c r="A58" s="27" t="inlineStr">
@@ -3052,15 +3083,19 @@
       </c>
       <c r="F58" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G58" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H58" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H58" s="48" t="inlineStr">
+        <is>
+          <t>migrations/tenant/0505, part 1. The KB §23.14 invariant ('a dictionary item cannot exist without at least one complete posting rule') was enforced by a constraint trigger AFTER INSERT ON dictionary_item only — it stopped you creating a rule-less item and did nothing about deleting the last rule out from under one that already existed. Consequence is not cosmetic: an item with no posting rule has no account to post to, so a costing line referencing it fails at posting time, long after the delete, in a different module, with an error naming neither. Closed from the other side with a DEFERRABLE constraint trigger AFTER DELETE OR UPDATE on posting_rule. DEFERRABLE matching 0200, so a legitimate replace-all-rules transaction still works — the check runs at COMMIT. AFTER UPDATE too, because re-pointing a rule's dictionary_item_id orphans the old item just as surely as deleting it. Skips the check when the item itself is gone, since deleting an item with its rules is legitimate.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="25">
       <c r="A59" s="27" t="inlineStr">
@@ -3888,15 +3923,19 @@
       </c>
       <c r="F78" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G78" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H78" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H78" s="28" t="inlineStr">
+        <is>
+          <t>New shared/observability/business-metrics.js: six probes over data that already existed — invoices posted by status, journal entries, approvals pending bucketed by age, undelivered/DEAD orchestration events, ledger writes per hour, and depreciation rows posted with no entry (the one that would have caught DATA 5.5, where uptime was 100%, error rate zero, and the only symptom was a number that should have been rising and was flat). Required adding GAUGE support to metrics.js, which had counters and histograms only — modelling a level as a counter makes rate() meaningless and a decrease read as a process restart. Refreshes on a timer rather than per scrape, because a 15s poll across the fleet is its own load problem against the PERF S1 connection budget. A failing tenant is reported AS a metric (collect_ok 0) rather than breaking the endpoint — proven with an unreachable tenant in the fleet, and with a probe whose table does not exist being skipped at debug.</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="25">
       <c r="A79" s="27" t="inlineStr">
@@ -4170,15 +4209,19 @@
       </c>
       <c r="F85" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G85" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H85" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H85" s="48" t="inlineStr">
+        <is>
+          <t>Two changes. (1) LEVEL: the eight paths the audit names as REAL swallowed failures move warn -&gt; error — costing-approval draft-invoice sync, email and push delivery (x2 each), approval notifications (x2), and AI usage/spend logging — so an alert keyed on level&gt;=error now sees them. Deliberately NOT a blanket conversion: a cache miss or a geocode timeout is a genuine degrade, and promoting those would drown the eight that matter. (2) STACKS: `{ err: err.message }` discards the stack, which was the other half of the finding. All 74 call sites across 49 files now pass the Error object, so pino's default err serializer keeps type, message and stack. Applied only inside logger.* calls — `err: err.message` feeding a jsonb column or an error-report payload is left alone, because an Error there serialises to '{}' and converting would LOSE the message rather than gain a stack. REDACT_PATHS already censors err.detail, so the pg-error leak stays closed.</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="25">
       <c r="A86" s="27" t="inlineStr">
@@ -4754,15 +4797,19 @@
       </c>
       <c r="F99" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G99" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H99" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H99" s="48" t="inlineStr">
+        <is>
+          <t>Lifecycle transitions were gated four different ways. All twelve flat-gated modules now use the shared requireTransitionPermission with a declared TRANSITION_ACTION map, validator FIRST so the target state is checked against the enum before it selects its own gate. The split follows the design the helper already documents: ADVANCING a record is `edit`; a decision that ends it, or that is irreversible outside the system (DISPATCHED, SIGNED, CLOSED, DONE, CANCELLED), is `approve`. Unlisted states fall back to `approve` — fails closed. purchase_request.routes.js's local reimplementation of the helper is deleted in favour of the shared import. One deliberate LOOSENING, flagged: proposal was flat `approve` for every target, so only approvers could SUBMIT — the exact bug PERMISSION_SWEEP_BACKLOG §A and the helper's own header describe. DRAFT/IN_REVIEW/SENT relax to `edit`; REJECTED stays `approve`.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="25">
       <c r="A100" s="27" t="inlineStr">
@@ -4792,15 +4839,19 @@
       </c>
       <c r="F100" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G100" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H100" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H100" s="48" t="inlineStr">
+        <is>
+          <t>doc/API_REFERENCE.md, GENERATED by scripts/generate-api-docs.js from doc/api-contract.json — the artefact check-api-contract.js already derives by mounting the real routers, and which CI already fails on. All 731 routes across 100 modules, grouped by prefix, with body-validation status. Critically it also documents THE OUT-OF-BAND REQUEST CONTRACT, which F-25 called out as underivable by an integrator: Host selects the tenant, X-Praxis-Env selects the sandbox schema for business data only, identity always resolves against LIVE so a TEST flip never logs you out, X-Request-Id correlation, and the list/filter/sort vocabulary. A generated spec cannot disagree with the code the way the 19%-complete Postman collection had. `--check` mode catches drift. NOT included: the access-tier table — see API-F23.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="34.5" customHeight="1" s="25">
       <c r="A101" s="27" t="inlineStr">
@@ -4914,15 +4965,19 @@
       </c>
       <c r="F103" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G103" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H103" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H103" s="48" t="inlineStr">
+        <is>
+          <t>FOUND BY TC-C12's chain test, not by inspection: asserting one error envelope across four failure modes showed the tenant-gate 404 had no request_id at all. hostTenantResolver (TENANT_NOT_FOUND / TENANT_SUSPENDED / TENANT_NOT_READY), tenantContext (NO_TENANT_CONTEXT) and feature-gate (NO_TENANT_CONTEXT / FEATURE_DISABLED) all answered with res.status(...).json(...) directly, bypassing the error handler — so the six failures a customer is most likely to phone about ('unknown workspace', 'workspace suspended', 'that feature is off') were the six they could not quote a correlation id for. Fixed STRUCTURALLY rather than by adding the field at six sites that would drift again: all six now go through next(new AppError(code, message, status)), so they inherit the standard envelope, the log line they never had, and — for the 500s — the error report. Status codes and error codes are unchanged, asserted explicitly. Verified: middleware-chain.test.js asserts request_id === the X-Request-Id header on all four gate failures and that the 404/403/423 contract is preserved; auth-middleware, rbac-enforcement and capability-assignment (62 assertions) re-run green.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="25">
       <c r="A104" s="27" t="inlineStr">
@@ -4952,15 +5007,19 @@
       </c>
       <c r="F104" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G104" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H104" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H104" s="48" t="inlineStr">
+        <is>
+          <t>A tenant-API request on a platform host (localhost, api.*, admin.*, the apex) hit tenantContext with no req.tenant and answered 500 NO_TENANT_CONTEXT — a server error for a client mistake, and a documented footgun (postman/README warns 'localhost is the platform host'). tenantContext now distinguishes the two causes it was conflating: req.isPlatform means the resolver ran and deliberately set no tenant -&gt; 400 WRONG_HOST with a message naming the correct host and the X-Praxis-Tenant dev header. No tenant AND not a platform host still means a misordered middleware chain and stays a loud, logged, reported 500. Owner chose 400 over keeping the status.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1" s="25">
       <c r="A105" s="27" t="inlineStr">
@@ -5218,15 +5277,19 @@
       </c>
       <c r="F111" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G111" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H111" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H111" s="48" t="inlineStr">
+        <is>
+          <t>`update: create.partial()` made the status field patchable wherever create declared it, so PATCH /:id {status} reached a state change under plain `edit` while POST /:id/status might require `approve` — the transition gate was effectively optional, and tightening F-21 alone would have moved the hole rather than closed it. New shared middleware requireLifecyclePermissionOnPatch mounted on the PATCH route of all eleven affected resources: when the body does not carry the lifecycle field it does nothing at all, so ordinary edits are untouched; when it does, the request must satisfy the SAME permission the dedicated endpoint requires for that target state. A caller holding the right permission is unaffected; only the cheaper path 403s, which is the escalation closing. Owner chose enforce-now over shadow-mode.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1" s="25">
       <c r="A112" s="27" t="inlineStr">
@@ -5256,15 +5319,19 @@
       </c>
       <c r="F112" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G112" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H112" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H112" s="48" t="inlineStr">
+        <is>
+          <t>Two halves. (1) THE AUTHZ BUG: `react` and `star` took a bare messageId and asserted nothing, so any MOD-64 `view` holder could react to or star ANY message in ANY channel including ones they cannot see — and a reaction is broadcast over the realtime channel, so it doubled as a way to announce presence in a private conversation. `listMembers` likewise had no assert, disclosing any channel's roster. Added assertMessageMember (resolves message -&gt; channel, then the existing assertMember) and an assert on listMembers; the controller now passes the actor. Not-a-member and no-such-message return the SAME 403, so the message id is not disclosed. (2) THE CONTRACT: eight write endpoints were gated `view`, so granting a role MOD-64 view also granted 'add and remove channel members'. Writes to SHARED state (archive, add/remove member, edit/delete another's message) now require `edit`. Own-preference writes (pin, mute, read marker, draft, star, react) deliberately KEEP `view` and say so in writing — they are per-user rows keyed on the caller, and requiring a write grant to mute a channel you can already read would be the opposite mistake. Membership remains the real authorisation throughout.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="25">
       <c r="A113" s="27" t="inlineStr">
@@ -5302,7 +5369,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H113" s="28" t="n"/>
+      <c r="H113" s="48" t="inlineStr">
+        <is>
+          <t>ATTEMPTED AND DELIBERATELY NOT SHIPPED. The intent was to publish the self-scoped tier in the generated API reference. doc/api-contract.json records auth/rbac per route from the middleware NAMES on that route's own stack, but nearly every router applies authentication once via router.use(authMiddleware), which never appears on an individual route — so the flags read auth:false for hundreds of routes that ARE authenticated. Classifying tiers off them produced '713 public, 9 self-scoped' against the audit's 10 and 61. A security tier table that lies is worse than none, so the section was removed and replaced with an explicit statement of why, pointing at API_CONTRACT_AUDIT §F-23/F-24 as the reference meanwhile. Closing this properly means resolving router-level middleware inside check-api-contract.js so CI and the doc share one answer — a contained change, but it belongs to that script, not to a doc generator.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="25">
       <c r="A114" s="27" t="inlineStr">
@@ -5332,15 +5403,19 @@
       </c>
       <c r="F114" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G114" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H114" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H114" s="48" t="inlineStr">
+        <is>
+          <t>Unknown query keys were dropped silently, so `?stat=OPEN` returned the UNFILTERED list and looked like it had worked — a filter typo silently widened the result set. makeRepo now takes `filterable`; anything outside it (plus the shared limit/offset/q/sort vocabulary) is 422 UNKNOWN_FILTER naming the key and listing what is available. Declared on the 16 repos that use makeRepo's list unchanged — that list only ever honoured limit/offset/q, so every other key was already being ignored, which IS the finding. Repos that override list() keep current behaviour until their filters are declared, so nothing that works today breaks.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="25">
       <c r="A115" s="27" t="inlineStr">
@@ -5370,15 +5445,19 @@
       </c>
       <c r="F115" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G115" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H115" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H115" s="48" t="inlineStr">
+        <is>
+          <t>No endpoint accepted a sort parameter; order was fixed at makeRepo config time, so any consumer wanting a different order fetched and sorted client-side — and by F-26/F-27 that meant sorting a truncated 50-row window, i.e. sorting the wrong rows. `?sort=col` / `?sort=-col` now resolves through an explicit `sortable` allow-list (declared on all 24 makeRepo repos), validated and quoted via query-helpers.ident. An unlisted column is 422 INVALID_SORT listing what is sortable — refused, never interpolated, because ORDER BY built from user input is exactly the injection SEC H3 closed.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1" s="25">
       <c r="A116" s="27" t="inlineStr">
@@ -5408,15 +5487,19 @@
       </c>
       <c r="F116" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G116" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H116" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H116" s="48" t="inlineStr">
+        <is>
+          <t>doc/ERROR_CODES.md, GENERATED from source by scripts/generate-api-docs.js: 219 AppError codes with raise counts and HTTP statuses, plus the shared error-envelope shape. The six near-synonyms the audit named (BAD_AMOUNT/INVALID_AMOUNT, BAD_STATE/BAD_STATUS, EMPLOYEE_NOT_FOUND/NOT_FOUND, FORBIDDEN + NOT_YOURS + NOT_A_MEMBER/PERMISSION_DENIED) are published as ALIASES, deliberately not renamed — a code a client already switches on cannot be changed without breaking it, and enumerating them is the precondition for ever retiring them. `--check` mode fails if the committed file drifts from the code.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="25">
       <c r="A117" s="27" t="inlineStr">
@@ -5728,15 +5811,19 @@
       </c>
       <c r="F124" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G124" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H124" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H124" s="28" t="inlineStr">
+        <is>
+          <t>New repo.preferencesFor / insertForUsers / activeEmailsFor and service.notifyMany. The fan-out called notify() per recipient, each issuing ~5 queries — for 50 finance users on invoice.posted (a normal path, it is on the allowlist) that is ~250 SEQUENTIAL round-trips while holding a write transaction open, pinning one of eight pooled connections and extending the lock window on the business row. Now a fixed 4 queries regardless of recipient count: one preference read for everyone across both channels, one multi-row INSERT via unnest (parameterised, so the statement text does not change with recipient count and the plan cache still works), one address lookup. MEASURED: 50 recipients went from ~250 round-trips to 2. Email/push sends deliberately stay in the caller's transaction — moving them out means deciding what happens when the transaction rolls back after an email has gone, which is a correctness question and a separate change.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1" s="25">
       <c r="A125" s="27" t="inlineStr">
@@ -5766,15 +5853,19 @@
       </c>
       <c r="F125" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G125" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H125" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H125" s="28" t="inlineStr">
+        <is>
+          <t>emitEvent's first act on every create/update/archive across 93 modules was a SELECT on event_type — a STATIC SEEDED CATALOGUE, read on every single write and never cached. Now an in-process cache keyed by (tenant, key), because event_type is a tenant table and a global cache would let one tenant's catalogue answer another's question — the same mistake PERF S9 was about. 5-minute TTL so a process running since before a seeding migration notices within a deploy cycle; unknown keys cache as null too, since a nonexistent event type is a stable fact and not caching it leaves the hot path uncached for exactly the keys someone typo'd. Bounded at 5000 entries. MEASURED: 100 writes of the same event type went from 100 catalogue reads to 1, and a second tenant correctly missed.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="25">
       <c r="A126" s="27" t="inlineStr">
@@ -6090,15 +6181,19 @@
       </c>
       <c r="F133" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G133" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H133" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H133" s="48" t="inlineStr">
+        <is>
+          <t>auth-context.tsx passed an inline object literal as the provider value containing six handlers re-created on every render, so every render of AuthProvider produced a new context identity and re-rendered every consumer — and with zero React.memo across 134 components there was nothing to arrest the cascade. AuthProvider wraps the whole app, so that is every render of everything. All six handlers are now React.useCallback with empty deps (they close only over stable setters and module helpers; patchUser uses the functional setUser form, which is why it needs no user dep) and the value is useMemo'd, so its identity changes only when the auth state genuinely does. branding-context.tsx had the same shape and gets the same treatment. tsc --noEmit clean.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1" s="25">
       <c r="A134" s="27" t="inlineStr">
@@ -6128,15 +6223,19 @@
       </c>
       <c r="F134" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G134" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H134" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H134" s="48" t="inlineStr">
+        <is>
+          <t>HALF OF THIS WAS ALREADY DONE and the register did not say so: client/src/lib/use-resource.ts is no longer the hand-rolled hook the audit describes — it has been migrated to TanStack Query (staleTime 30s, gcTime 5m, refetchOnWindowFocus), so caching, request dedup and stale-while-revalidate are in place across all 150+ call sites. What remained was the second half: app-shell.tsx's badge poller, a raw setInterval(load, 60000) OUTSIDE the cache, two requests per user per minute forever — the audit's arithmetic puts that at ~33 req/s of pure badge polling at 1,000 users and ~230 DB round-trips/second, on a topology with a 12-connection-per-tenant ceiling. Now a useQuery with refetchInterval 60s, refetchIntervalInBackground FALSE (most of that traffic was tabs nobody was looking at) and staleTime 30s, so the two requests are deduplicated across every component wanting a badge. refetchOnWindowFocus means returning to the tab refreshes immediately, so the badge is fresher on return while costing less in between. env is in the query key so a LIVE/TEST flip reads the right counts.</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1" s="25">
       <c r="A135" s="27" t="inlineStr">
@@ -6166,15 +6265,19 @@
       </c>
       <c r="F135" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G135" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H135" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H135" s="48" t="inlineStr">
+        <is>
+          <t>migrations/tenant/0504, part 2. pg_trgm GIN indexes on the 41 (table, column) pairs reachable by ILIKE — the 8 declared via makeRepo searchColumn plus 33 hand-rolled in module repos. A leading wildcard cannot use a B-tree, so every free-text search was a sequential scan; the audit measured 66.96ms -&gt; 4.55ms (14.7x) with no query rewrite, since the same SQL simply becomes indexable. The pair list was derived by static analysis and a `col ILIKE` inside a joining function cannot always be attributed to the right table from source alone, so rather than ship a list I could not fully verify — and fail the migration for every tenant on the first wrong pair — each index is created only if the column exists and is a text type, with a NOTICE naming any pair that does not resolve. That is explicitly NOT `EXCEPTION WHEN OTHERS THEN NULL` (DATA 3.6): the precondition is tested, and anything unexpected still aborts.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15" customHeight="1" s="25">
       <c r="A136" s="27" t="inlineStr">
@@ -6280,15 +6383,19 @@
       </c>
       <c r="F138" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G138" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H138" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H138" s="48" t="inlineStr">
+        <is>
+          <t>The identical hand-rolled `update()` SET builder was copy-pasted into 46 module repos. All 46 now call query-helpers.updateOne; zero remain (verified by grep). 39 were converted by a codemod that refuses anything it does not recognise exactly, and the 7 it reported were done by hand — including three genuinely different shapes (an arrow returning a promise chain, an object method using `this`, and one whose RETURNING is a module constant). updateOne gained an `opts.touch` option because appending `, updated_at = now()` was the sole reason most of them existed. Generated SQL verified byte-equivalent to the originals apart from identifier quoting.</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1" s="25">
       <c r="A139" s="27" t="inlineStr">
@@ -6318,15 +6425,19 @@
       </c>
       <c r="F139" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G139" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H139" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H139" s="48" t="inlineStr">
+        <is>
+          <t>The audit traced no live vulnerability and neither did I — but its point was that the helper should not depend on every caller being careful, and the real finding turned out to be sharper than 'defence in depth'. SEC H3 had already hardened query-helpers with identifier validation and an optional writable allow-list; what nobody had noticed is that the 46 repos in PERF-S19 BYPASSED IT ENTIRELY by building their own SET clause, so the hardening covered only the modules that happened to route through updateOne. Deduplicating those 46 is what makes it universal — S19 is the delivery mechanism for S20, not a separate tidy-up. Also fixed the one identifier still interpolated raw in that file: getById's `pk`. Verified: identifier injection now raises INVALID_FIELD and an out-of-list column raises FIELD_NOT_WRITABLE, on every repo.</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1" s="25">
       <c r="A140" s="27" t="inlineStr">
@@ -6650,15 +6761,19 @@
       </c>
       <c r="F147" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G147" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H147" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H147" s="28" t="inlineStr">
+        <is>
+          <t>tests/unit/money-path.test.js — 22 assertions running determination.compute FOR REAL against OHADA account codes: balance on every shape, VAT at 19.25% to the centime, receivable on the debit side of a sale (getting it backwards inverts the balance sheet and still balances), debours excluded from the taxable base (taxing it overstates output VAT to the revenue authority — a filing error, not just an invoice error), the purchase mirror, multi-line rounding where each line's VAT rounds independently, no zero-value legs, and all 9 refusal codes. Two of my own assertions were WRONG and the code was stricter than I assumed: toCents refuses sub-centime precision rather than rounding it, and refuses negative amounts rather than posting a contra. Both are better contracts than I expected and the tests now assert the real ones.</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15" customHeight="1" s="25">
       <c r="A148" s="27" t="inlineStr">
@@ -6688,15 +6803,19 @@
       </c>
       <c r="F148" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G148" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H148" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H148" s="28" t="inlineStr">
+        <is>
+          <t>The four integration suites were never disabled by anyone — they self-skip on `!process.env.DATABASE_URL`, and nothing ever set it. journal-posting.test.js says so in its own header: 'Run in CI by adding a postgres service + db:provision, then set these vars.' The new migrations job is exactly that, so it now seeds a corporate_entity and the BQ/VT/AC/OD journals (not seeded by 9000-9060 — they are business data, not reference data) and runs the suites against the real database. The step asserts the PASS COUNT, not just the exit code, because Jest exits 0 on a run where every suite skipped — 'it passed' and 'it ran' are different questions and only one was ever being asked. mail-imap.test.js stays opt-in on live IMAP/SMTP credentials, which is correct: a test that talks to a third-party mail server does not belong in every PR run.</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1" s="25">
       <c r="A149" s="27" t="inlineStr">
@@ -6726,15 +6845,19 @@
       </c>
       <c r="F149" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G149" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H149" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H149" s="48" t="inlineStr">
+        <is>
+          <t>tests/unit/wms-inventory.test.js — 35 assertions on inventory.service and outbound.service. The three failures DATA 5.1 describes are concurrency and atomicity failures, so a canned fake would have passed against the BROKEN code just as happily as the fixed code (the objection TC-Q3 raises about the existing regex fakes). This file therefore does NOT mock the repo: it runs the real repo SQL against a small in-memory Postgres implementing per-row FOR UPDATE locks, delta-applied-to-stored-value semantics, the `qty_on_hand + $2 &gt;= 0` guard, and real BEGIN/COMMIT/ROLLBACK. That makes the actual failures testable: two concurrent -5 and -3 moves against 10 end at 2 (not 7 — the reported lost update) and genuinely serialise; two concurrent -6 against 10 let exactly ONE through and leave the balance at 4 with one journal row; twenty interleaved moves keep qty_on_hand equal to the sum of the journal and never negative; moves on DIFFERENT items do not serialise (row lock, not table lock); a failed move releases its lock. Also: the journal write failing rolls the balance back, the event write failing rolls both back, nested moves join one transaction rather than committing it early (DATA 5.2), and both state machines are asserted exhaustively as tables (14 stock transitions, 12 outbound). MUTATION-VERIFIED: restoring the pre-DATA-5.1 read-modify-write move() fails 9 of the 35, including both race tests. Two fixture defects were found and fixed while writing this — a rollback that truncated the journal to a high-water mark (which rolled back a CONCURRENT transaction's committed work) and a non-re-entrant row lock that self-deadlocked nested moves; both are commented in place.</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1" s="25">
       <c r="A150" s="27" t="inlineStr">
@@ -6764,15 +6887,19 @@
       </c>
       <c r="F150" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G150" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H150" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H150" s="48" t="inlineStr">
+        <is>
+          <t>tests/unit/orchestration-outbox.test.js — all 10 assertions now pass end to end (previously 7-8 then an undiagnosed hang, which is why this was left Partially fixed). THE HANG WAS NOT A HANG. `jest.resetModules()` in beforeEach made every one of the ten tests rebuild the dispatcher's require graph, which is 171 modules because dispatcher.js requires ./handlers at load. Measured: ~6s per rebuild on a mounted filesystem, ~8.3s cold — ten tests is ~60s, so the file died around test seven or eight with no failure and no summary. Diagnosed by requiring the dispatcher in a bare node process: it leaves ZERO active handles beyond stdio and the process exits cleanly, so there is no leaked timer or connection — the previous session's stated suspicion was the wrong premise. The reset is also unnecessary: the dispatcher holds no module-level mutable state (every sweep's state is on the client the caller passes) and resolves handlers through registry.getHandlers() at dispatch time, so the mock picks up each test's handler list with nothing reloaded. Fix: require the dispatcher once at file load, keep only `handlers = []` in beforeEach. Runtime 60s+ -&gt; 8.5s. The jest.setup.js ALERT_WEBHOOK_URL/ALERT_EMAIL fix from the previous session stands and is unrelated.</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1" s="25">
       <c r="A151" s="27" t="inlineStr">
@@ -6802,15 +6929,19 @@
       </c>
       <c r="F151" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G151" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H151" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H151" s="48" t="inlineStr">
+        <is>
+          <t>tests/unit/tenant-provisioning.test.js — 52 assertions on provisioning.service, the code scripts/deploy.sh runs against every tenant on every deploy. Concentrated on the three behaviours that are themselves fixes for other findings and had no coverage: (1) DATA 3.2 fleet containment — a failing tenant no longer aborts the sweep, asserted by failing the MIDDLE of three and proving the third was still migrated, that each tenant is enumerated with which side of the line it fell on, and that it still throws FLEET_MIGRATION_PARTIAL afterwards so a deploy goes red; (2) the citext[] depends_on trap — toDepsArray parses the raw Postgres literal ('{}' -&gt; [], never ['{','}']), enforceDependencies cascades to a fixpoint through a chain and in any row order, an unknown dependency counts as unmet, source is preserved while state flips, and the query still carries the ::text[] cast; (3) SEC H6 on createAdmin, which mints the CEO account that bypasses every permission check. Also: slug rejection (it becomes a database name), unknown plan refused before the tenant goes LIVE, provisioning order, both schemas migrated, secret_ref is a pointer not a password, wipeSandbox clearing ONLY the sandbox migration scopes, and fleetSchemaStatus reporting an unreachable tenant rather than failing the report. MUTATION-VERIFIED: five simultaneous mutations (abort-on-first-failure, dropped ::text[] cast, single-pass fixpoint, removed SEC H6 check, full ledger wipe) fail 11 of the 52. Two honest notes: a dependency CYCLE is left on rather than off — recorded in the test, unreachable from the current catalogue, not claimed as a finding; and wipeSandbox's non-transactionality (DI-5.6, still Open) is asserted as current behaviour so whoever fixes it sees the test fail deliberately.</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15" customHeight="1" s="25">
       <c r="A152" s="27" t="inlineStr">
@@ -6840,15 +6971,19 @@
       </c>
       <c r="F152" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G152" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H152" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H152" s="48" t="inlineStr">
+        <is>
+          <t>tests/unit/portal-auth.test.js — 45 assertions across portal_auth.service AND portal_auth.middleware, which is where the grant is actually enforced. Four properties: (1) a portal token is not a staff token — both are signed with JWT_ACCESS_SECRET so typ is the entire boundary, asserted from both directions (staff access token, 2FA-pending token and refresh-secret-signed token all refused, at the service AND at the gate); (2) the token carries identity only and portal_access is re-read per request, asserted by pulling the grant between two calls with the SAME token and getting 403; (3) failures do not enumerate — unknown email / wrong password / disabled account produce one error, and unknown / used / expired / empty invite tokens produce one error, asserted by comparing the errors to EACH OTHER rather than to a string literal; (4) SEC H6 holds — 'password' and '12345678', the two that passed the old `length &lt; 8` check, are named explicitly. Also covers invite lifetimes (7 days vs 30 minutes, 0482), one-live-link-at-a-time, tokens stored hashed, a weak password NOT consuming the invite, mail failure preserving both the login and the token, and a disabled account being re-activated on re-invite. argon2, jwt and the password policy are real; only the repo, mailer and portal-access lookup are mocked. MUTATION-VERIFIED: removing the typ check, the SEC H6 policy call, the grant check and the ACTIVE-status check fails 10 of the 45.</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="15" customHeight="1" s="25">
       <c r="A153" s="27" t="inlineStr">
@@ -6878,15 +7013,19 @@
       </c>
       <c r="F153" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G153" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H153" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H153" s="48" t="inlineStr">
+        <is>
+          <t>tests/unit/middleware-chain.test.js — 42 assertions sending real HTTP through supertest into a real Express app with the real chain (requestId -&gt; hostTenantResolver -&gt; tenantContext -&gt; authMiddleware -&gt; requirePermission -&gt; controller). Express, the router, the async-safe shim and all five middlewares are real; only the tenant registry and identity cache are mocked. Asserts what only a chain can: ORDER (tenantContext without the resolver, and auth without tenantContext, both 500 rather than proceeding tenant-less, and the identity cache is never reached); SHORT-CIRCUIT (a SUSPENDED tenant is 403 and a PROVISIONING tenant 423 even when a perfectly valid token is presented — asserted WITH a valid token, and getAuthUser is never called); PERF S2 (exactly ONE connection checkout for a request where auth, rbac and the controller all read — the fix was for three, capping concurrency at pool_max/3 — plus zero checkouts for a route that touches no database, and a search_path re-bind rather than a second checkout under sandbox); OBS-E3 (the correlation id from header to ambient context to error body, client-supplied ids adopted, over-long ones rejected); OBS-L3 (auth back-filling userId into the context tenantContext bound before it); SEC-C2 sid; the LIVE/TEST toggle not logging the user out; CEO bypass; and `=== true` grant comparison rejecting a truthy 1. Two hosts resolve to two tenants in one process.</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="15" customHeight="1" s="25">
       <c r="A154" s="27" t="inlineStr">
@@ -6916,15 +7055,19 @@
       </c>
       <c r="F154" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G154" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H154" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H154" s="48" t="inlineStr">
+        <is>
+          <t>tests/unit/auth-refresh-flow.test.js — 22 assertions on refresh() ITSELF, not on its extracted predicate. The audit's objection was that a refactor dropping the refreshTokenReused call site would leave all five existing predicate tests passing; PROVEN BY MUTATION: disabling that call site fails 3 of the new tests and 0 of the 5 old ones. Covers typ-confusion (an access token presented as a refresh token), wrong-secret rejection, expiry, killed session, subject/session mismatch, reuse-of-a-rotated-away-token asserted END TO END (rotate once, replay the original — no reference to the predicate by name), that revocation is complete (row killed + Redis removed + identity cache invalidated + LOGGED_OUT with reason refresh_token_reuse), that a revoked session is not simultaneously rotated or touched, legacy NULL-jti grandfathering, the 30-min inactivity kill and its exact boundary (the check is &gt; not &gt;=), keep_signed_in opting out of the idle kill but NOT out of revocation (0494), NaN-safe idle handling, and sid surviving rotation (SEC-C2). Two further mutations verified: dropping sid from the rotated access token and widening the idle window each fail exactly the test that names them. JWT is real throughout — tokens are signed and verified with the configured secrets.</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1" s="25">
       <c r="A155" s="27" t="inlineStr">
@@ -6954,15 +7097,19 @@
       </c>
       <c r="F155" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G155" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H155" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H155" s="28" t="inlineStr">
+        <is>
+          <t>Same file. final-invoice-lifecycle.test.js mocks determination and journal_entry.service, so it asserts the lifecycle and NOTHING about the accounting — which is correct for a lifecycle test; the missing half was a test of the arithmetic itself. That half now exists and is unmocked. The balance assertion is the load-bearing one: assert_entry_balanced in the database is the final authority but fires at INSERT time, by which point the failure surfaces as a 500 from inside a posting.</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="15" customHeight="1" s="25">
       <c r="A156" s="27" t="inlineStr">
@@ -6992,15 +7139,19 @@
       </c>
       <c r="F156" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G156" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H156" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H156" s="28" t="inlineStr">
+        <is>
+          <t>New `migrations` job: postgres:16 service, real platform migrate, a tenant provisioned from nothing (the path a new customer takes, never previously run in CI), then the tenant set applied a SECOND time asserting zero files applied — the migrator's idempotency claim rests entirely on its schema_migration ledger and nothing checked it. Then probe-doc-numbers, because 0498's unique indexes have no NOT VALID escape and either build or fail the whole run. This is the worst asymmetry in the audit: every other gate's worst outcome is a broken feature; a migration's is a half-migrated production database at the moment deploy.sh has already rolled the old image away.</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="15" customHeight="1" s="25">
       <c r="A157" s="27" t="inlineStr">
@@ -7030,15 +7181,19 @@
       </c>
       <c r="F157" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G157" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H157" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H157" s="28" t="inlineStr">
+        <is>
+          <t>docker-build now STARTS the image and waits for /api/health, then asserts every module mounts inside it. The image was built and never run, so anything between `docker build` succeeding and the process serving reached production untouched — which is not hypothetical: the deps stage did not copy packages/, so the image shipped with @praxis/shared unresolvable and NO INVOICING MODULE, and it built perfectly. Liveness only, because /api/health deliberately touches no dependency and is the one question a container with no database can answer. Runs with NODE_ENV=production — verified the throwaway CI secrets satisfy env.js's production guard, which rejects the dev-default ENCRYPTION_KEY and identical access/refresh secrets.</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1" s="25">
       <c r="A158" s="27" t="inlineStr">
@@ -7068,15 +7223,19 @@
       </c>
       <c r="F158" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G158" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H158" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H158" s="28" t="inlineStr">
+        <is>
+          <t>npm ci everywhere (4 sites). The old comment justified `install` on the grounds that the lockfile is Windows-generated so `ci` could omit linux binaries — THE PREMISE IS FALSE and was worth checking rather than inheriting: lockfileVersion 3 records every platform variant regardless of the generating machine, verified that this lockfile contains @img/sharp-linux-x64, @img/sharp-libvips-linux-x64, argon2 and node-gyp-build. The cost of the old line is the finding: `npm install` may resolve NEWER versions than the lockfile pins, so CI tested a dependency tree that is neither what the Dockerfile builds nor what deploys.</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="15" customHeight="1" s="25">
       <c r="A159" s="27" t="inlineStr">
@@ -7106,15 +7265,19 @@
       </c>
       <c r="F159" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G159" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H159" s="28" t="n"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H159" s="28" t="inlineStr">
+        <is>
+          <t>Same fix as DI-3.2 — this finding IS the containment half. Per-tenant error capture, an enumerated result, a FLEET_MIGRATION_PARTIAL error carrying the full outcome, and a read-only status command that names who is behind and who is unreachable (which are different problems: unreachable is not behind, and migrating an unreachable tenant is not the remedy).</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1" s="25">
       <c r="A160" s="27" t="inlineStr">
@@ -9410,27 +9573,27 @@
         </is>
       </c>
       <c r="B5" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A5,Register!$D$2:$D$206,B$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A5,Register!$D$2:$D$500,B$4)</f>
         <v/>
       </c>
       <c r="C5" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A5,Register!$D$2:$D$206,C$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A5,Register!$D$2:$D$500,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A5,Register!$D$2:$D$206,D$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A5,Register!$D$2:$D$500,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A5,Register!$D$2:$D$206,E$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A5,Register!$D$2:$D$500,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A5,Register!$D$2:$D$206,F$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A5,Register!$D$2:$D$500,F$4)</f>
         <v/>
       </c>
       <c r="G5" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A5,Register!$D$2:$D$206,G$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A5,Register!$D$2:$D$500,G$4)</f>
         <v/>
       </c>
       <c r="H5" s="46">
@@ -9445,27 +9608,27 @@
         </is>
       </c>
       <c r="B6" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A6,Register!$D$2:$D$206,B$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A6,Register!$D$2:$D$500,B$4)</f>
         <v/>
       </c>
       <c r="C6" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A6,Register!$D$2:$D$206,C$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A6,Register!$D$2:$D$500,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A6,Register!$D$2:$D$206,D$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A6,Register!$D$2:$D$500,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A6,Register!$D$2:$D$206,E$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A6,Register!$D$2:$D$500,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A6,Register!$D$2:$D$206,F$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A6,Register!$D$2:$D$500,F$4)</f>
         <v/>
       </c>
       <c r="G6" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A6,Register!$D$2:$D$206,G$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A6,Register!$D$2:$D$500,G$4)</f>
         <v/>
       </c>
       <c r="H6" s="46">
@@ -9480,27 +9643,27 @@
         </is>
       </c>
       <c r="B7" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A7,Register!$D$2:$D$206,B$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A7,Register!$D$2:$D$500,B$4)</f>
         <v/>
       </c>
       <c r="C7" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A7,Register!$D$2:$D$206,C$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A7,Register!$D$2:$D$500,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A7,Register!$D$2:$D$206,D$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A7,Register!$D$2:$D$500,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A7,Register!$D$2:$D$206,E$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A7,Register!$D$2:$D$500,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A7,Register!$D$2:$D$206,F$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A7,Register!$D$2:$D$500,F$4)</f>
         <v/>
       </c>
       <c r="G7" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A7,Register!$D$2:$D$206,G$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A7,Register!$D$2:$D$500,G$4)</f>
         <v/>
       </c>
       <c r="H7" s="46">
@@ -9515,27 +9678,27 @@
         </is>
       </c>
       <c r="B8" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,B$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A8,Register!$D$2:$D$500,B$4)</f>
         <v/>
       </c>
       <c r="C8" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,C$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A8,Register!$D$2:$D$500,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,D$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A8,Register!$D$2:$D$500,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,E$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A8,Register!$D$2:$D$500,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,F$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A8,Register!$D$2:$D$500,F$4)</f>
         <v/>
       </c>
       <c r="G8" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A8,Register!$D$2:$D$206,G$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A8,Register!$D$2:$D$500,G$4)</f>
         <v/>
       </c>
       <c r="H8" s="46">
@@ -9550,27 +9713,27 @@
         </is>
       </c>
       <c r="B9" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,B$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A9,Register!$D$2:$D$500,B$4)</f>
         <v/>
       </c>
       <c r="C9" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,C$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A9,Register!$D$2:$D$500,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,D$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A9,Register!$D$2:$D$500,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,E$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A9,Register!$D$2:$D$500,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,F$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A9,Register!$D$2:$D$500,F$4)</f>
         <v/>
       </c>
       <c r="G9" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A9,Register!$D$2:$D$206,G$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A9,Register!$D$2:$D$500,G$4)</f>
         <v/>
       </c>
       <c r="H9" s="46">
@@ -9585,27 +9748,27 @@
         </is>
       </c>
       <c r="B10" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,B$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A10,Register!$D$2:$D$500,B$4)</f>
         <v/>
       </c>
       <c r="C10" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,C$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A10,Register!$D$2:$D$500,C$4)</f>
         <v/>
       </c>
       <c r="D10" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,D$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A10,Register!$D$2:$D$500,D$4)</f>
         <v/>
       </c>
       <c r="E10" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,E$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A10,Register!$D$2:$D$500,E$4)</f>
         <v/>
       </c>
       <c r="F10" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,F$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A10,Register!$D$2:$D$500,F$4)</f>
         <v/>
       </c>
       <c r="G10" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A10,Register!$D$2:$D$206,G$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A10,Register!$D$2:$D$500,G$4)</f>
         <v/>
       </c>
       <c r="H10" s="46">
@@ -9620,27 +9783,27 @@
         </is>
       </c>
       <c r="B11" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,B$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A11,Register!$D$2:$D$500,B$4)</f>
         <v/>
       </c>
       <c r="C11" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,C$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A11,Register!$D$2:$D$500,C$4)</f>
         <v/>
       </c>
       <c r="D11" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,D$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A11,Register!$D$2:$D$500,D$4)</f>
         <v/>
       </c>
       <c r="E11" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,E$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A11,Register!$D$2:$D$500,E$4)</f>
         <v/>
       </c>
       <c r="F11" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,F$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A11,Register!$D$2:$D$500,F$4)</f>
         <v/>
       </c>
       <c r="G11" s="46">
-        <f>COUNTIFS(Register!$B$2:$B$206,$A11,Register!$D$2:$D$206,G$4)</f>
+        <f>COUNTIFS(Register!$B$2:$B$500,$A11,Register!$D$2:$D$500,G$4)</f>
         <v/>
       </c>
       <c r="H11" s="46">
@@ -9714,7 +9877,7 @@
         </is>
       </c>
       <c r="B15" s="46">
-        <f>COUNTIF(Register!$F$2:$F$206,$A15)</f>
+        <f>COUNTIF(Register!$F$2:$F$500,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="46" t="n"/>
@@ -9731,7 +9894,7 @@
         </is>
       </c>
       <c r="B16" s="46">
-        <f>COUNTIF(Register!$F$2:$F$206,$A16)</f>
+        <f>COUNTIF(Register!$F$2:$F$500,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="46" t="n"/>
@@ -9748,7 +9911,7 @@
         </is>
       </c>
       <c r="B17" s="46">
-        <f>COUNTIF(Register!$F$2:$F$206,"Fixed")</f>
+        <f>COUNTIF(Register!$F$2:$F$500,"Fixed")</f>
         <v/>
       </c>
       <c r="C17" s="46" t="n"/>
@@ -9765,7 +9928,7 @@
         </is>
       </c>
       <c r="B18" s="46">
-        <f>COUNTIF(Register!$F$2:$F$206,$A18)</f>
+        <f>COUNTIF(Register!$F$2:$F$500,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="46" t="n"/>
@@ -9782,7 +9945,7 @@
         </is>
       </c>
       <c r="B19" s="46">
-        <f>COUNTIF(Register!$F$2:$F$206,$A19)</f>
+        <f>COUNTIF(Register!$F$2:$F$500,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="46" t="n"/>
@@ -9799,7 +9962,7 @@
         </is>
       </c>
       <c r="B20" s="46">
-        <f>COUNTIF(Register!$G$2:$G$206,"Verified in code")</f>
+        <f>COUNTIF(Register!$G$2:$G$500,"Verified in code")</f>
         <v/>
       </c>
       <c r="C20" s="46" t="n"/>

--- a/doc/AUDIT_REGISTER_2026-08-04.xlsx
+++ b/doc/AUDIT_REGISTER_2026-08-04.xlsx
@@ -692,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="24" min="1" max="1"/>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="H133" s="48" t="inlineStr">
         <is>
-          <t>auth-context.tsx passed an inline object literal as the provider value containing six handlers re-created on every render, so every render of AuthProvider produced a new context identity and re-rendered every consumer — and with zero React.memo across 134 components there was nothing to arrest the cascade. AuthProvider wraps the whole app, so that is every render of everything. All six handlers are now React.useCallback with empty deps (they close only over stable setters and module helpers; patchUser uses the functional setUser form, which is why it needs no user dep) and the value is useMemo'd, so its identity changes only when the auth state genuinely does. branding-context.tsx had the same shape and gets the same treatment. tsc --noEmit clean.</t>
+          <t>auth-context.tsx passed an inline object literal as the provider value containing six handlers re-created on every render, so every render of AuthProvider produced a new context identity and re-rendered every consumer — and with zero React.memo across 134 components there was nothing to arrest the cascade. AuthProvider wraps the whole app, so that is every render of everything. The handlers are now useCallback'd and the value useMemo'd, so identity changes only when auth state genuinely does. branding-context.tsx had the same shape and gets the same treatment. CORRECTION 2026-08-05: the first pass gave ALL SIX handlers an empty dep array, and two of them read render state — verify2fa reads pendingToken, registerPin reads user. Empty arrays capture the first render's values forever, both of which are null: verify2fa would have sent pending_token: null so 2FA could never complete, and registerPin's `if (user)` branch would never run, so the server would register a PIN device the browser never recorded and the next PIN login would fail NO_PIN_DEVICE against a device that exists. A stale-closure bug in the auth path, introduced by this fix and caught by eslint react-hooks/exhaustive-deps, which the same session's CI run surfaced. Both now carry their dependency; the other four are genuinely stable and stay []. acceptTokens is deliberately not a dep — it closes over nothing from render scope, and listing it would make three handlers unstable every render and undo S14 for no behavioural gain. The comment in the file that asserted all six were stable has been corrected — it had become a description of code that no longer matched. eslint clean on the file; client tsc --noEmit clean.</t>
         </is>
       </c>
     </row>
@@ -9417,10 +9417,10 @@
         </is>
       </c>
     </row>
-    <row r="213">
+    <row r="213" s="25">
       <c r="A213" s="24" t="inlineStr">
         <is>
-          <t>NEW-06</t>
+          <t>NEW-07</t>
         </is>
       </c>
       <c r="B213" s="24" t="inlineStr">
@@ -9456,6 +9456,132 @@
       <c r="H213" s="24" t="inlineStr">
         <is>
           <t>Found 2026-08-05 while verifying the incident runbook's containment steps against the real routes. Every other write on session.routes.js carries requirePermission(MODULE, ...) — create, update, archive — and this one does not. Session ids are uuids so it is not trivially enumerable, but a session id leaks into logs and error payloads more readily than a password does, and the effect is forced logout of an arbitrary user (nuisance, or targeted denial of access to an approver mid-workflow). The sibling route /mine/revoke-all is correctly ungated because it is self-scoped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" s="25">
+      <c r="A214" s="24" t="inlineStr">
+        <is>
+          <t>NEW-08</t>
+        </is>
+      </c>
+      <c r="B214" s="24" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C214" s="24" t="inlineStr">
+        <is>
+          <t>dossier has no `title` column, yet both services that open a dossier from a won opportunity write one — the sales→operations handoff has never worked by either route</t>
+        </is>
+      </c>
+      <c r="D214" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E214" s="24" t="inlineStr">
+        <is>
+          <t>Code + migration</t>
+        </is>
+      </c>
+      <c r="F214" s="24" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G214" s="24" t="inlineStr">
+        <is>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H214" s="24" t="inlineStr">
+        <is>
+          <t>Found 2026-08-05 the first time the integration job ran against a real Postgres (TC-CI6). 0310 created dossier with no title and the only ALTER since (0479) adds pol/pod_place_id, but orchestration/handlers/opportunity-won-open-dossier.js:48 and sales/opportunity.service.js:62 both pass title: opp.name. insertOne builds its column list from Object.keys(data) and validates each key as an IDENTIFIER, which 'title' is — so it reached Postgres and returned 42703. TWO failure modes: the event route rolls back inside the outbox, retries to DEAD, and returns 200 to the user (opportunity marked WON, no dossier, no link — Operations never sees the job); the synchronous route POST /opportunities/:id/win with createDossier:true is not swallowed and 500s, so that flag has never once succeeded. The downstream costing 'dossier_id violates not-null' failures are the same defect one step later. FIX: migration 0508 adds the column (nullable) + backfills from opportunity.name where a dossier was linked by hand, chosen over deleting the argument because both call sites are carrying the deal name across the one boundary where Operations needs it and dossier's only other label is the machine-allocated ref. Also declared a `writable` allow-list on the dossier repo — the layer that would have caught this, since the zod validator strips unknown keys but BOTH broken call sites reach service.create in-process with no HTTP anywhere near them. tests/unit/dossier-columns.test.js reconciles that list and both call-site payloads against the columns the migrations declare, with no DB, so the next mismatch fails in the fast suite. CAVEAT, stated plainly: 0508 has NOT been executed — this session has no Postgres and no libpg-query, so it is unparsed and unapplied. Confirmation is `npm run db:migrate:tenants` then the orchestration integration suite. Not committed; left in the working tree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" s="25">
+      <c r="A215" s="24" t="inlineStr">
+        <is>
+          <t>NEW-09</t>
+        </is>
+      </c>
+      <c r="B215" s="24" t="inlineStr">
+        <is>
+          <t>Test &amp; CI/CD</t>
+        </is>
+      </c>
+      <c r="C215" s="24" t="inlineStr">
+        <is>
+          <t>The integration fixture never satisfied the contract the integration suites document, and a negative test passed for the wrong reason for its whole life</t>
+        </is>
+      </c>
+      <c r="D215" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E215" s="24" t="inlineStr">
+        <is>
+          <t>Config + tests</t>
+        </is>
+      </c>
+      <c r="F215" s="24" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G215" s="24" t="inlineStr">
+        <is>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H215" s="24" t="inlineStr">
+        <is>
+          <t>Found 2026-08-05 on the first real run of the integration job. THREE distinct defects, one cause — the fixture was written from what the suites obviously needed rather than from what their headers say they need. (1) NO accounting_period was seeded, though both suites document one: journal-posting failed 'No accounting period covers &lt;today&gt;' and ledger-hardening's beforeAll left `period` undefined, so all six of its tests died on `period.period_id` — six identical 'Cannot read properties of undefined' failures naming the reader, not the cause. (2) Both suites posted to account 521, which is the PARENT 'Banques locales' with is_postable=false; 5211 'Banque principale' is the leaf. The service refused it with 'account 521 is not postable (KB 23.3)' — the rule working correctly. (3) Worst of the three: journal-posting's 'rejects an unbalanced entry' asserted only `.rejects.toThrow()`, so it PASSED on the not-postable error and never once reached the balance check it is named after. A negative test that cannot say why it failed will pass for the wrong reason indefinitely. FIX: ci.yaml seeds an OPEN calendar-month period around CURRENT_DATE (computed in SQL, so it cannot drift from the runner clock) and ASSERTS exactly one covers today before running anything; both suites post to 5211; the unbalanced test now asserts /Out of balance/; ledger-hardening's beforeAll throws a message naming the missing fixture instead of letting six tests fail on the symptom. NOT RUN: this session has no Postgres, so ci.yaml is YAML-validated and the suites parse-checked only — the job itself is the verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" s="25">
+      <c r="A216" s="24" t="inlineStr">
+        <is>
+          <t>NEW-10</t>
+        </is>
+      </c>
+      <c r="B216" s="24" t="inlineStr">
+        <is>
+          <t>Test &amp; CI/CD</t>
+        </is>
+      </c>
+      <c r="C216" s="24" t="inlineStr">
+        <is>
+          <t>Client spies typed as ReturnType&lt;typeof vi.spyOn&gt; erased the signature, so nine test fixtures could omit required fields of the type they stood in for</t>
+        </is>
+      </c>
+      <c r="D216" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E216" s="24" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="F216" s="24" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G216" s="24" t="inlineStr">
+        <is>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H216" s="24" t="inlineStr">
+        <is>
+          <t>Surfaced when the client was pinned to vitest ^3 to match vite 5 and `tsc -b` failed on use-list-paged.test.tsx and use-resource.test.tsx. `ReturnType&lt;typeof vi.spyOn&gt;` names the generic WITHOUT instantiating it, so it resolves to MockInstance&lt;(this: unknown, ...args: unknown[]) =&gt; unknown&gt; — the uninstantiated default. MockInstance is invariant in its parameter, so the real spy would not assign to it. It compiled under vitest 4 by accident of that major's typings. FIXED by typing from the function being spied on (MockInstance&lt;typeof apiClient.tenantPaged&gt;), which is both more precise and indifferent to the vitest major. THAT CHANGE THEN REVEALED THE REAL DEFECT: every mockResolvedValue passed { data, total } only, while Paged&lt;T&gt; also requires limit, offset and hasMore — the API F-26 metadata added so a list screen could stop presenting the first 50 rows as the whole set. The fake had been handing the hook undefined for all three and nothing could complain, because the erased type let mockResolvedValue accept anything at all. Same shape as TC-Q3 from a different angle: a fake that cannot disagree with the contract it replaces. A `paged()` helper now fills the envelope; no assertion changed, because no test reads those three — which is the point. DECISION RECORDED: stay on vite 5 + vitest 3 rather than moving to vite 7 + vitest 4. The forward path keeps these two files untouched but is a build-tool major that cannot be verified without a real build, and PERF-S8 (a Vite config change needing exactly that) is already open. Client `tsc --noEmit` is clean across all of src. The vitest RUN could not be executed here: node_modules was installed on Windows so @rollup/rollup-linux-x64-gnu is absent.</t>
         </is>
       </c>
     </row>

--- a/doc/AUDIT_REGISTER_2026-08-04.xlsx
+++ b/doc/AUDIT_REGISTER_2026-08-04.xlsx
@@ -1153,15 +1153,19 @@
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G11" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H11" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H11" s="28" t="inlineStr">
+        <is>
+          <t>authMiddleware now enforces the `sid` SEC-C2 put in the token. THE NAIVE FIX IS WORSE THAN THE BUG: Redis is a cache, user_session.killed_at is the record, so a restart/eviction/FLUSHDB empties the index while every session in it is still valid — rejecting on 'absent from Redis' would sign out every user of every tenant the first time Redis blinked. session-store gains a THREE-VALUED isSessionActive (true/false/null): true = live; false = ask Postgres; null = index unreachable, conclude nothing. Happy path is one Redis EXISTS and NO SQL (asserted by query count, not by outcome — the outcome alone would pass a regression that queried every request). A cold index costs one indexed query. Fails OPEN and loudly if both layers are down: refusing every request would turn a cache outage into a total sign-out, and the 15-minute window this closes is not worth that. Legacy tokens with no sid pass and expire on their own, so this does not sign out active users mid-deploy. tests/unit/session-revocation.test.js — 6 tests, all six branches of the matrix; mutation-verified (disabling the check fails exactly the two rejection cases). One test bug found and fixed while writing it: it counted identityDb calls, which the user projection also uses, instead of SQL calls.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="25">
       <c r="A12" s="27" t="inlineStr">
@@ -1233,15 +1237,19 @@
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H13" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>GET /documents/:id and /:id/download required MOD-64 view and nothing else. The vault holds contracts, payslips, ID documents and signed PDFs across HR, finance and operations, so anyone granted MOD-64 for any legitimate reason — an operations clerk reading shipping paperwork — could enumerate and download EVERY document in the tenant, including HR files about colleagues. field_visibility masks fields and has no document analogue; the /media mount was already correctly gated and the gap was the granularity behind it. Now gated on the OWNING module resolved from the record's doc_type via moduleKeyForDocType, the same principle as document-templates and approval_task.module_key (0488): a payslip needs the payroll grant, a purchase request MOD-62. THE IMPLEMENTATION DIFFERENCE that mattered: template.routes.js reads docType from the URL, so the module is known before any I/O; here it is a column on the row, so the record must be LOADED FIRST and the grant checked against what it turns out to be — that ordering is the whole middleware. MOD-64 still passes, deliberately: it is the vault administrator's grant and revoking it in the same change would lock out the people whose job is the vault, a silent outage dressed as a security fix. What changed is that MOD-64 is no longer the ONLY way in and no longer a skeleton key across departments. CEO bypass retained, matching every other gate. Absent record falls through to the controller's own 404 rather than leaking existence through the authorisation path. Routes load clean; both re-verify as tier 'gated' in the contract snapshot.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="25">
       <c r="A14" s="27" t="inlineStr">
@@ -1271,15 +1279,19 @@
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G14" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H14" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>realtime/index.js read `auth.host || headers.host`, so a socket client CHOSE which tenant its token resolved against. It failed closed only because a user id from tenant A does not exist in tenant B's app_user — isolation resting on UUID non-collision, which stops being true the moment any tenant DB is restored, cloned or seeded from another (staging refresh, support copy), and would then fail OPEN silently. NOT removed outright: `auth.host` is a documented DEVELOPMENT affordance (comms-socket.ts: 'in dev, pass host/url overrides') because the Vite dev server proxies the socket, so the Host header is the dev server's, not the tenant subdomain's — deleting it would have closed the hole and broken every developer's local socket. Gated on NODE_ENV !== production, exactly as the origin check above it already gates devLocal: same rule, same place. Production now matches the HTTP path, which resolves tenant from Host alone.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="25">
       <c r="A15" s="27" t="inlineStr">
@@ -1317,7 +1329,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H15" s="28" t="n"/>
+      <c r="H15" s="28" t="inlineStr">
+        <is>
+          <t>OPEN. One project with SEC-M7 and TC-E3 — see handoff §18C. Individually these read as Mediums; together they are the answer to 'what happens after a credential compromise', which today is everything, everywhere.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="25">
       <c r="A16" s="27" t="inlineStr">
@@ -1347,15 +1363,19 @@
       </c>
       <c r="F16" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G16" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="inlineStr">
+        <is>
+          <t>The platform tier has a session now. It was STATELESS: no session table, so no remote kill, no rotation-reuse detection, and a 30-day refresh TTL inherited from the shared default — on the tier that provisions and wipes tenant databases and holds the credential store. The only revocation lever was deactivating the user, effective at the NEXT refresh, so a stolen platform refresh token stayed usable for up to 30 days after anyone noticed. The asymmetry was backwards: the tenant tier has had all of this since SEC-C2, and the MORE privileged tier was the LESS protected one. Migration 0070 adds platform.platform_session, mirroring tenant user_session on purpose rather than inventing a second design — same kill semantics (killed_at/killed_by), same rotation chain (replaced_by) — so the reuse logic reads identically in both places and a reviewer learns it once. Unique index on refresh_jti (every refresh resolves by it), partial index on live rows per user. auth.service.js: refresh tokens now carry sid+jti and name their session row; login opens a session recording ip/user-agent; refresh resolves the session and refuses killed, expired or already-rotated ones, then rotates by setting replaced_by. REUSE DETECTION is what earns the table — a refresh for an already-replaced session means the token was captured, so killChain() kills the whole recursive chain rather than just refusing the request, because refusing one request leaves the attacker's NEWER token working. killSession() and listSessions() added. TTL cut from the shared 30d to 7d (PLATFORM_REFRESH_TTL), deliberately not the tenant value: 30 days is reasonable for a warehouse clerk's phone and not for a credential that administers every customer. TWO DEFENSIVE CHOICES worth noting. (a) Tokens minted before this ships carry no sid and are accepted ONCE without a session, rotating onto a real one — otherwise deploying signs out every platform admin mid-shift; the grace ends by itself. (b) The TTL is converted to a Postgres interval explicitly and VALIDATED AT LOAD: a first version used replace(/^(\d+)d$/) which silently passed '12h' through unchanged, and a malformed interval would have reached the database and failed every platform LOGIN at runtime — the worst place to find a config typo. It now rejects what it cannot convert, at boot, with the fix in the message. Verified across 7d/12h/30m/2w plus a garbage value. NOT INCLUDED: platform 2FA still returns 501. The column exists and the audit asks for the step-up, but that is a feature build (pending-token design, enrolment, recovery codes) rather than the revocation gap this finding is mostly about — and it is the same undecided design as the tenant side. Migration is unapplied in this session (no Postgres); reversibility and destructive-statement gates pass.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="25">
       <c r="A17" s="27" t="inlineStr">
@@ -1393,7 +1413,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H17" s="28" t="n"/>
+      <c r="H17" s="28" t="inlineStr">
+        <is>
+          <t>OPEN. One project with SEC-M5 and TC-E3 — see handoff §18C. Per-tenant DB roles resolved through secret_ref, per-tenant data keys wrapped by a master key, and a rotation path.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="25">
       <c r="A18" s="27" t="inlineStr">
@@ -1423,7 +1447,7 @@
       </c>
       <c r="F18" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G18" s="31" t="inlineStr">
@@ -1433,7 +1457,7 @@
       </c>
       <c r="H18" s="28" t="inlineStr">
         <is>
-          <t>server.js: script-src ['self','unsafe-inline'], script-src-attr ['unsafe-inline']</t>
+          <t>`unsafe-inline` removed from script-src and script-src-attr; helmet's defaults restored ('self' / 'none'). THE REASON FOR THE EXCEPTION NO LONGER EXISTED. It was relaxed application-wide for one feature: the Control Tower rendered the Lovable mock in an &lt;iframe srcDoc&gt; that inherited the page CSP, with an inline &lt;script&gt; bridge and inline onclick= handlers. PHASE 3 / AUDIT F1 DELETED THAT IFRAME — the Control Tower is real React now and the onclick handlers survive only in comments describing what the mock used to do. So the primary XSS mitigation had been switched off across every page including login, for months, protecting nothing — and with the refresh token in web storage (SEC-L3) a single XSS bought 30 days of account access. Worth recording as a pattern: a documented, deliberate exception outlived its justification silently, because nothing ties an exception to the thing that justified it. VERIFIED BEFORE REMOVING, since this fails closed and visibly if wrong: both index.html files carry exactly one script each and it is external (type=module src=/src/main.tsx); vite-plugin-pwa is configured injectRegister:false so no inline registration script is emitted, and the built dist/index.html has one script tag; the two remaining srcDoc iframes (document preview, template preview) use sandbox="" and sandbox="allow-same-origin" — neither grants allow-scripts, so scripts cannot run in them and they need no script-src. img-src stays relaxed: tenant-authored branding legitimately points at external https URLs and blob:/data: are used by generated previews.</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1489,7 @@
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G19" s="31" t="inlineStr">
@@ -1475,7 +1499,7 @@
       </c>
       <c r="H19" s="28" t="inlineStr">
         <is>
-          <t>ci.yaml:79 continue-on-error: true on npm audit</t>
+          <t>The third leg of M9 — nothing watched for NEW advisories (TC-CI4 made the audit gate block with a dated expiry; this is the monitoring). .github/dependabot.yml covers npm at root/client/platform-console, plus github-actions and docker. WEEKLY AND GROUPED, deliberately: a bot opening fifteen PRs a week gets muted, and a muted bot is worse than none because it still looks like coverage. Minor+patch grouped per ecosystem, majors separate because they need a decision (the exceljs major behind the current findings is exactly that). open-pull-requests-limit 3 for the same reason. Commit prefixes match the conventional-commit PR-title gate added under TC-R4, so Dependabot's own PRs pass CI. vite/vitest majors are IGNORED — pinned as a pair (vitest 4 needs vite 6/7), so an automated bump of either alone would reintroduce the breakage documented in handoff §14. .github/workflows/codeql.yaml adds SAST: javascript-typescript, security-extended, on push/PR plus a weekly schedule. Extended rather than the default set because SEC-H3 (request-body keys becoming SQL identifiers) is precisely CodeQL's js/sql-injection shape and that class is not hypothetical here — it has already happened once. Separate workflow, not a step in ci.yaml, because it needs security-events: write and widening the build job's permissions is the wrong trade. Both files YAML-validated.</t>
         </is>
       </c>
     </row>
@@ -1507,15 +1531,19 @@
       </c>
       <c r="F20" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G20" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H20" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="inlineStr">
+        <is>
+          <t>Dockerfile runtime and worker stages now `chown -R node:node /app` and `USER node` (uid 1000 already exists in node:*-alpine). Compose bind-mounts ./data — the document vault, holding contracts, payslips and ID documents — plus ./media, ./uploads and ./logs into both, so a root-owned process meant an RCE-class bug reached the host filesystem with full rights over all of it. THE OPERATIONAL HALF IS THE PART THAT BREAKS A DEPLOY IF SKIPPED: a bind-mounted host directory keeps its host ownership inside the container, so without a chown the app boots cleanly and fails its FIRST WRITE at runtime — a green deploy that breaks on the first user. scripts/deploy.sh now mkdir -p's and chowns those four paths to 1000:1000 before rolling containers, idempotently, with a printed manual command if it cannot (unprivileged deploy user). The first run after this ships performs the one-off repair of files earlier root containers created. deploy.sh passes bash -n; the image itself could NOT be built in this session (no Docker).</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.25" customHeight="1" s="25">
       <c r="A21" s="27" t="inlineStr">
@@ -1545,15 +1573,19 @@
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H21" s="28" t="inlineStr">
+        <is>
+          <t>TWO of the three parts were ALREADY CLOSED by PERF-S9 and it is worth saying so rather than re-fixing them: the identity-cache keyspace is namespaced per tenant, and invalidateGrants no longer uses a blocking KEYS sweep that flushed every tenant's grants on any one tenant's permission edit. What remained was authentication. docker-compose now starts Redis with --requirepass "${REDIS_PASSWORD:?...}" — the `:?` form so compose REFUSES TO START when it is unset, because `--requirepass ""` is a no-op that looks configured and authenticates nothing, which is the exact 'control that is counted but does not bite' shape this remediation keeps finding. The loopback binding was a real mitigation and is one compose edit from not being one (publish the port, add a host, use network_mode: host) — and the cache holds the session index, identity/RBAC projections and RATE-LIMIT COUNTERS, the last of which matter more than they sound: writable counters mean the login limiter can be reset at will, quietly undoing SEC-C3. The healthcheck authenticates too, or it would report a container healthy that no client can use. REDIS_PASSWORD documented in .env.example with the both-places warning, and declared in env.js — the TC-E1 gate CAUGHT the omission when it was added, which is the gate working.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="23.25" customHeight="1" s="25">
       <c r="A22" s="27" t="inlineStr">
@@ -1591,7 +1623,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H22" s="28" t="n"/>
+      <c r="H22" s="28" t="inlineStr">
+        <is>
+          <t>NOT ATTEMPTED, deliberately, and the reasoning has changed since the audit — which is the useful part. L3's severity was explicitly COUPLED to SEC-M8 (unsafe-inline CSP) and SEC-C2 (the refresh token was never revoked). BOTH ARE NOW CLOSED: script-src is back to helmet's defaults so the XSS that would read web storage is materially harder, and C2 plus SEC-M1 mean a stolen token is revocable and dies with its session. The residual is real but smaller than when it was written. WHY NOT DONE: it is a coordinated client+server contract change with no safe half. Moving the refresh token to an httpOnly cookie means CSRF protection on every state-changing route, `credentials: 'include'` throughout the client, a CORS posture change from permissive to exact-origin, and — the part that actually needs a decision — a COOKIE SCOPE STORY ACROSS TENANT SUBDOMAINS: tenants are &lt;slug&gt;.&lt;domain&gt;, so a cookie scoped to the apex is shared by every tenant in the browser while a host-scoped cookie breaks any cross-subdomain flow. Portal and platform tiers each have their own refresh path and would need the same treatment. A partially migrated refresh path is worse than either end state, and none of it is exercisable in this session — the failure mode of getting it subtly wrong is a total lockout on deploy. It needs the cookie-scope decision first; after that it is a bounded piece of work.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="23.25" customHeight="1" s="25">
       <c r="A23" s="27" t="inlineStr">
@@ -1663,15 +1699,19 @@
       </c>
       <c r="F24" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Partially fixed</t>
         </is>
       </c>
       <c r="G24" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="inlineStr">
+        <is>
+          <t>Shares API-F23's mechanism, as planned in handoff §15. The effective-middleware walk that L5 needs now exists in check-api-contract.js and is correct for the tenant surface; doc/api-contract.json records a per-route tier, so 'which routes are reachable without credentials' is now a queryable fact rather than a grep for authMiddleware anywhere in a router. Three anonymous/generically-named auth gates were found and named in the process (see F23). NOT CLOSED: the per-route CI assertion with an explicit allow-list is not wired, because it must not be built on the platform-tier classification while that is still wrong — a gate asserting the wrong tiers is worse than the shallow test it replaces. tests/unit/auth-coverage.test.js remains per-ROUTER and was separately hardened under TC-Q6 (identity matching, floor 50 to 95).</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="25">
       <c r="A25" s="27" t="inlineStr">
@@ -2801,7 +2841,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H51" s="28" t="n"/>
+      <c r="H51" s="28" t="inlineStr">
+        <is>
+          <t>OPEN by design — correctly diagnosed and correctly left alone. Handoff §18B.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="25">
       <c r="A52" s="27" t="inlineStr">
@@ -4049,15 +4093,19 @@
       </c>
       <c r="F81" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G81" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H81" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H81" s="28" t="inlineStr">
+        <is>
+          <t>scripts/db/check-destructive-migrations.js + CI step. deploy.sh applies migrations to EVERY tenant database before the app rolls; the convention 'keep them additive' was enforced by nothing (check-migration-numbers validates numbering, check-migration-reversibility validates a -- DOWN block exists — neither reads what the SQL does). NOT A BAN, because destructive migrations are sometimes right and a gate that forbids them gets worked around: it requires an explicit `-- DESTRUCTIVE: &lt;what is lost and why that is acceptable&gt;` on the line or the line above. The marker is the point — it forces the author to write the sentence, puts it in the diff for a reviewer, and leaves it in the file for whoever is restoring a backup at 02:00. Covers DROP TABLE/COLUMN/SCHEMA, TRUNCATE, DELETE FROM, ALTER COLUMN TYPE and SET NOT NULL (the last two fail loudly on non-conforming data, which on a per-tenant migrator strands the estate on different schema versions). Deliberately ignores DROP INDEX/TRIGGER/FUNCTION IF EXISTS — recreated by the same migrations that drop them, destroy no rows, and matching them would make the marker meaningless through frequency. Mutation-verified 4 ways: unmarked DROP COLUMN fails; the same marked passes; DROP INDEX IF EXISTS passes; a DROP inside a comment passes. Clean on the current tree. The pre-deploy backup (already in deploy.sh) is the other half of I3.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="25">
       <c r="A82" s="27" t="inlineStr">
@@ -4087,17 +4135,17 @@
       </c>
       <c r="F82" s="35" t="inlineStr">
         <is>
-          <t>Partially fixed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G82" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
+          <t>Verified in code</t>
         </is>
       </c>
       <c r="H82" s="28" t="inlineStr">
         <is>
-          <t>Smoke test can now fail and the deploy exits non-zero. Auto-rollback NOT wired — rollback.sh has never been executed, and automating an unproven recovery path is worse than manual.</t>
+          <t>The readiness gate was already real (/api/health/ready probes Postgres and Redis, replacing a curl that could not fail). What was missing is the REVERT: a failed gate left the non-serving build in place and printed a command for a human, and deploy.sh runs unattended from CI, so 'someone will read the log' is not a control. AUTO_ROLLBACK=1 now calls rollback.sh, records 'failed-rolled-back', and announces that the SCHEMA is still forward. OPT-IN, and that is the substance of the fix rather than a hedge: migrations have already run by this point and this repo has no down-migrations before 0500 (DI-3.5), so reverting CODE under a schema that moved is safe for an additive migration and NOT safe otherwise — an automatic revert could turn a broken deploy into a corrupted one. That is a judgement about the specific change, so the operator makes it once in the deploy environment instead of the script guessing every time. Default OFF preserves today's behaviour exactly.</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4185,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H83" s="28" t="n"/>
+      <c r="H83" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — owner action. Infrastructure spend, not code. Handoff §18A.</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="25">
       <c r="A84" s="27" t="inlineStr">
@@ -5057,7 +5109,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H105" s="28" t="n"/>
+      <c r="H105" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — part of the API-contract cluster (F7-F14). ONE decision sitting, then one mechanical batch; piecemeal is worse than not at all. Handoff §18D. Concretely confirmed this session: /portals is the internal admin module and /portal is the external product, and they are genuinely different things sharing a near-identical prefix.</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="25">
       <c r="A106" s="27" t="inlineStr">
@@ -5095,7 +5151,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H106" s="28" t="n"/>
+      <c r="H106" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — API-contract cluster (F7-F14). Handoff §18D.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="25">
       <c r="A107" s="27" t="inlineStr">
@@ -5133,7 +5193,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H107" s="28" t="n"/>
+      <c r="H107" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — API-contract cluster (F7-F14). Handoff §18D.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="25">
       <c r="A108" s="27" t="inlineStr">
@@ -5171,7 +5235,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H108" s="28" t="n"/>
+      <c r="H108" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — API-contract cluster (F7-F14). Handoff §18D.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="25">
       <c r="A109" s="27" t="inlineStr">
@@ -5209,7 +5277,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H109" s="28" t="n"/>
+      <c r="H109" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — API-contract cluster (F7-F14). Handoff §18D.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1" s="25">
       <c r="A110" s="27" t="inlineStr">
@@ -5247,7 +5319,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H110" s="28" t="n"/>
+      <c r="H110" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — API-contract cluster (F7-F14). Handoff §18D.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1" s="25">
       <c r="A111" s="27" t="inlineStr">
@@ -5361,17 +5437,17 @@
       </c>
       <c r="F113" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Partially fixed</t>
         </is>
       </c>
       <c r="G113" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
+          <t>Verified in code</t>
         </is>
       </c>
       <c r="H113" s="48" t="inlineStr">
         <is>
-          <t>ATTEMPTED AND DELIBERATELY NOT SHIPPED. The intent was to publish the self-scoped tier in the generated API reference. doc/api-contract.json records auth/rbac per route from the middleware NAMES on that route's own stack, but nearly every router applies authentication once via router.use(authMiddleware), which never appears on an individual route — so the flags read auth:false for hundreds of routes that ARE authenticated. Classifying tiers off them produced '713 public, 9 self-scoped' against the audit's 10 and 61. A security tier table that lies is worse than none, so the section was removed and replaced with an explicit statement of why, pointing at API_CONTRACT_AUDIT §F-23/F-24 as the reference meanwhile. Closing this properly means resolving router-level middleware inside check-api-contract.js so CI and the doc share one answer — a contained change, but it belongs to that script, not to a doc generator.</t>
+          <t>THE BLOCKER IS FIXED; the classification is not yet trustworthy enough to publish, and that distinction is the whole finding. (1) THE WALK. check-api-contract.js read auth/rbac from each route's OWN stack, but nearly every router does `router.use(authMiddleware)` once at the top — a layer with no .route whose .handle has no .stack, so the walk hit neither branch and dropped it. Hundreds of authenticated routes recorded auth:false, which is why the first tier table said '713 public, 9 self-scoped'. The walk now carries router-level middleware down, accumulating IN ORDER (correct as well as convenient: Express applies a `use` only to routes registered after it, so a public route declared above the auth line still reports public — exactly the mistake worth catching). Result: 19 public / 94 self-scoped / 624 gated, against 713/9/rest before. (2) THREE REAL BUGS FOUND BY DOING IT, all the same shape — an authorisation gate invisible because its function had no useful name. portal_auth.middleware.js returned an ANONYMOUS function, so GET /portal/me, /client, /investor and /auditor — the entire external portal product — classified as PUBLIC. platform-auth.js's requirePlatformRole and requireCap both returned a function called `check`, too generic to recognise. All three are now named (portalAuthCheck, platformRoleCheck, platformCapCheck). These were live blind spots in any inventory of 'what is reachable without credentials', not merely tooling noise. (3) VERIFIED: the 19 public routes were listed and read individually — auth endpoints, login-screen branding, the documented /scan, OAuth callbacks and webhooks. All legitimate. (4) NOT DONE, deliberately: ~23 /api/platform/* routes still classify self-scoped, including DELETE /platform/tenants/... Their capability gates are applied somewhere this walk does not yet see. Publishing a tier table while that is unresolved would repeat the exact failure that kept F23 open — a SECURITY document that lies. The tier is recorded per-route in doc/api-contract.json so the data is visible in diffs; the DOC TABLE and the CI gate wait until platform classification is proven. Remaining: resolve platform, then emit the table in generate-api-docs.js (the section is written and suppressed) and fail CI on any public/self-scoped route not in an explicit allow-list.</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5613,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H117" s="28" t="n"/>
+      <c r="H117" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — API-contract cluster (F7-F14). Handoff §18D.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="25">
       <c r="A118" s="27" t="inlineStr">
@@ -5575,7 +5655,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H118" s="28" t="n"/>
+      <c r="H118" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — API-contract cluster (F7-F14). Handoff §18D.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="23.25" customHeight="1" s="25">
       <c r="A119" s="27" t="inlineStr">
@@ -5945,7 +6029,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H127" s="28" t="n"/>
+      <c r="H127" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — needs a real build to verify, so it needs your machine. PAIR IT WITH THE VITEST 4 MOVE (handoff §14): both are frontend build-tool changes and doing them separately means verifying the same build twice.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="15" customHeight="1" s="25">
       <c r="A128" s="27" t="inlineStr">
@@ -6151,7 +6239,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H132" s="28" t="n"/>
+      <c r="H132" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — a Chromium process per PDF. Bounded work (a pool), deferred only for session budget. Handoff §18E.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="25">
       <c r="A133" s="27" t="inlineStr">
@@ -6315,7 +6407,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H136" s="28" t="n"/>
+      <c r="H136" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — keyset pagination is a BREAKING change to the list contract, so it belongs with the API-contract decision sitting (§18D) rather than on its own.</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1" s="25">
       <c r="A137" s="27" t="inlineStr">
@@ -6345,15 +6441,19 @@
       </c>
       <c r="F137" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G137" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H137" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H137" s="28" t="inlineStr">
+        <is>
+          <t>A global limiter now sits in front of the API. Every pre-existing limiter guards ONE auth route (SEC-C3); beyond those a caller could issue unlimited requests, and on a single-host deployment one tenant's runaway integration consumed the Postgres, Redis and CPU that every other tenant is served from — with no signal until the box fell over. KEYED BY TENANT, then IP: keying on IP alone is wrong in both directions here, since an office behind one NAT looks like a single abusive client while a distributed integration for one tenant looks like a thousand innocent ones. The tenant is the unit of fairness because the tenant is what the capacity is shared between. Mounted AFTER the health, metrics and client-error routes and before the tenant router — the only placement that works, since a limiter that 429s /api/health/ready turns a busy minute into a failed deploy and a restarting container. Ceiling set high (600/min, RATE_LIMIT_API_PER_MIN) because it is a CIRCUIT BREAKER, not a quota: a gate that trips on legitimate use gets raised in a panic mid-incident and stops being a control. Reuses makeLimiter, so it inherits the Redis-backed store and the praxisRateLimit tag the structural tests read. Verified loaded and tagged.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="15" customHeight="1" s="25">
       <c r="A138" s="27" t="inlineStr">
@@ -7349,15 +7449,19 @@
       </c>
       <c r="F161" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Partially fixed</t>
         </is>
       </c>
       <c r="G161" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H161" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H161" s="28" t="inlineStr">
+        <is>
+          <t>THE REPO HALF ONLY, and the rest is not code. deploy.yaml now declares `environment: production`, which scopes the secrets, enables an approval gate and a deployment history, and gives the key one place to be rotated. Safe to land before the settings change: with no such Environment defined, GitHub falls back to repository secrets and the line is inert. NOT CLOSED — the finding is that CI holds a shell on production authenticated by one long-lived key, with the workflow's own docs giving `DEPLOY_USER e.g. root`. Remaining, all on the host or in GitHub settings: create the `production` Environment and move DEPLOY_HOST/DEPLOY_USER/DEPLOY_SSH_KEY into it with required reviewers; create an unprivileged `deploy` user with docker group membership and only the sudo entries deploy.sh needs; restrict the authorized_keys entry (from=, command=); set a rotation date. Until the user is unprivileged, a compromised Action is still a host compromise.</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="15" customHeight="1" s="25">
       <c r="A162" s="27" t="inlineStr">
@@ -7395,7 +7499,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H162" s="28" t="n"/>
+      <c r="H162" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — owner action, and it is ALREADY A COSTED DECISION (kickoff D6: no shared staging, on cost grounds). The finding is that SmartLS_PRD_Master_Functional_Spec_v2.md:215-216 still specifies 'Local -&gt; Staging -&gt; Production'. AMEND THE PRD so the team is not measured against a standard it consciously declined. Handoff §18A.</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="15" customHeight="1" s="25">
       <c r="A163" s="27" t="inlineStr">
@@ -7425,15 +7533,19 @@
       </c>
       <c r="F163" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G163" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H163" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H163" s="28" t="inlineStr">
+        <is>
+          <t>TWO halves, because the finding is about WHEN validation runs, not whether. (1) scripts/check-env-template.js reconciles .env.example against the Zod schema in env.js IN BOTH DIRECTIONS — a required key missing from the template (breaks a deploy) and a key the template documents that the schema no longer has (harmless at runtime, corrosive: it is how an operator sets a variable that does nothing). It reads the SCHEMA rather than a hand-kept list, so it cannot drift the way the template did. Wired into CI. Mutation-verified: removing a required key from the template makes it report and exit 1. A scanner defect was found and fixed while writing it — it read past the schema literal into INSECURE_DEFAULTS, whose UPPER_CASE keys are at the same indent; harmless today because those three are real schema keys, but the next uppercase constant added to env.js would have invented a required variable and failed CI for a key that does not exist. Now bounded to the z.object literal, and it throws if it parses implausibly few keys rather than passing vacuously. (2) deploy.sh now validates the environment in the freshly built image BEFORE migrations (`docker compose run --rm --no-deps api node -e "require('./src/config/env')"`). Previously env.js's guard ran at container start — deploy step 4-5, AFTER every tenant database had been migrated — so a change adding a required variable got as far as mutating all customer data before anything complained. bash -n clean.</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="15" customHeight="1" s="25">
       <c r="A164" s="27" t="inlineStr">
@@ -7513,7 +7625,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H165" s="28" t="n"/>
+      <c r="H165" s="28" t="inlineStr">
+        <is>
+          <t>OPEN — owner action. Follows from TC-CI1: switch on branch protection. The deploy-side guard already refuses to ship a commit that reached main without a PR. Handoff §18A.</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="23.25" customHeight="1" s="25">
       <c r="A166" s="27" t="inlineStr">
@@ -7585,15 +7701,19 @@
       </c>
       <c r="F167" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G167" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H167" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H167" s="28" t="inlineStr">
+        <is>
+          <t>coverageThreshold is expressed in FUNCTIONS, never lines or statements — that choice IS the finding. Lines measured 40.68% against functions 13.12% because 99 *.routes.js files report 100% statements with 0% functions: requiring the file registers the routes and that is all the statement counter sees. A line or statement gate would therefore be satisfied by IMPORTING files and would read healthy while measuring nothing. Set at 13, the figure the audit actually MEASURED, as a ratchet against regression rather than a target. NO `branches` floor: nobody has measured branch coverage here, and a guessed number either fails the build on arrival or passes forever meaninglessly — both end with the gate deleted. Add it once TC-CI3 has printed a real number.</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="15" customHeight="1" s="25">
       <c r="A168" s="27" t="inlineStr">
@@ -7623,15 +7743,19 @@
       </c>
       <c r="F168" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G168" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H168" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H168" s="28" t="inlineStr">
+        <is>
+          <t>final-invoice-lifecycle.test.js's fakeClient now THROWS on unrecognised SQL instead of returning { rows: [] }. The catch-all made the fake incapable of noticing anything: a wrong WHERE clause, a dropped tenant/entity filter, a changed column list, or a query never issued at all each arrived as 'no rows' and the test carried on. The proof was already in the file — a real query-shape change (PERF S20 quoting identifiers, so `WHERE "invoice_id"`) turned into 'Invoice not found' and the fake said nothing. An empty result is a LEGITIMATE answer to some queries and a SILENT FAILURE for the rest, and a catch-all cannot tell them apart. Every query the service issues must now be matched explicitly; adding one to the service means adding it here, which is the cost and is the point. Pattern taken from wms-inventory.test.js. Mutation-verified: breaking the invoice-lookup regex makes the suite fail with 'Unmatched SQL' rather than passing. Still a fake and still cannot prove the SQL is CORRECT — only the real database does that (TC-C6).</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="15" customHeight="1" s="25">
       <c r="A169" s="27" t="inlineStr">
@@ -7661,15 +7785,19 @@
       </c>
       <c r="F169" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G169" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H169" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H169" s="28" t="inlineStr">
+        <is>
+          <t>Both soft spots closed. (1) The guard matched middleware BY FUNCTION NAME (`l.name === 'authMiddleware'`), so renaming the function or wrapping it in asyncHandler — a normal thing to do to an async middleware — would leave every assertion passing while detecting nothing: it would report a fully authenticated surface on the day the surface went anonymous. It now compares against the IMPORTED FUNCTION REFERENCE, with the name check demoted to a visible secondary fallback for wrappers. The change is a strict superset of the old matcher (Express sets layer.name from handle.name), so it cannot fail anything that passed before. (2) The floor was `&gt; 50` while discovery returns 101 — verified in this session — so a module-loading regression to 51 would leave 49 routers unchecked while the suite stayed green, making 'module has no auth' indistinguishable from 'module was not looked at'. Floor pinned at 95. A third test asserts the import itself resolves, because if it ever yields undefined the identity check degrades silently to name-matching and defect (1) reopens. STILL PER-ROUTER, NOT PER-ROUTE — a router with one gated route and several ungated ones passes; that is SEC-L5 and wants the same effective-middleware walk as API-F23 (handoff §15). NOT EXECUTED: loading 101 routers exceeds this sandbox's per-command window.</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="15" customHeight="1" s="25">
       <c r="A170" s="27" t="inlineStr">
@@ -7699,15 +7827,19 @@
       </c>
       <c r="F170" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G170" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H170" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H170" s="28" t="inlineStr">
+        <is>
+          <t>The Test step was `npx jest --runInBand` — no coverage, no threshold, no report, no artifact, so the audit's numbers had to be produced by hand and nobody could see whether a change moved coverage at all. Now `jest --coverage` with a text-summary printed in the log and the lcov uploaded as an artifact (if: always(), because a threshold failure is exactly when you want the report). Threshold lives in jest.config.js.</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="15" customHeight="1" s="25">
       <c r="A171" s="27" t="inlineStr">
@@ -7779,15 +7911,19 @@
       </c>
       <c r="F172" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Partially fixed</t>
         </is>
       </c>
       <c r="G172" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H172" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H172" s="28" t="inlineStr">
+        <is>
+          <t>LINT NOW BLOCKS; there is still no backend type-check. `eslint .` was verified to exit 0 with warnings present because no-unused-vars and no-shadow are configured as 'warn', so between node --check (does it parse) and Jest (does this function work) there was no semantic gate: a typo in a property name on an untested path reached production. Now `eslint . --max-warnings 136` — a RATCHET at the measured count, not zero. Zero would fail on arrival and be reverted by whoever it blocked first, which is how a gate becomes a comment; the ceiling stops warnings growing and the edit that lowers it is the record that they were cleared. Three of the 136 were removed while doing this (console.log in the two new gate scripts — a check's own output should not push the ceiling up). NOT CLOSED: the backend is plain CommonJS with no type layer and adding one is a project, not a pipeline step. Worth recording that SmartLS_PRD_Master_Functional_Spec_v2.md:216 promises 'every merge runs lint + type-check + unit/integration tests' — the PRD and the pipeline still disagree, and the PRD is the thing that should move.</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="15" customHeight="1" s="25">
       <c r="A173" s="27" t="inlineStr">
@@ -7817,15 +7953,19 @@
       </c>
       <c r="F173" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G173" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H173" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H173" s="28" t="inlineStr">
+        <is>
+          <t>deploy.sh took `git pull --ff-only`, making deployment identity 'whatever main is when the script runs' — the commit whose CI went green is not necessarily the one that ships, and the workflow_dispatch path took no ref at all, so a manual deploy ALWAYS shipped current main. That is exactly backwards during an incident: the moment you most need a specific known-good commit is the moment main is the problem. DEPLOY_REF (env or $1) now pins it; blank keeps current-main so the automatic path is unchanged. `git fetch` + `checkout --detach` rather than pull: a detached checkout of an explicit SHA cannot fast-forward into something else and fails cleanly on a dirty tree, where a hand-edited tracked file used to make the deploy die mid-script under set -e at an arbitrary point, possibly after migrations. deploy.yaml gains a `ref` input. bash -n clean.</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="15" customHeight="1" s="25">
       <c r="A174" s="27" t="inlineStr">
@@ -7855,15 +7995,19 @@
       </c>
       <c r="F174" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G174" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H174" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H174" s="28" t="inlineStr">
+        <is>
+          <t>ci.yaml gains `concurrency: { group: ci-&lt;ref&gt;, cancel-in-progress: &lt;PR only&gt; }`. deploy.yaml already had one; CI did not, so two rapid pushes to main produced two runs, two workflow_run events and two deploys ordered by COMPLETION rather than commit order — the trigger SHA and deployed SHA then provably differ, which IS TC-R3. cancel-in-progress differs by branch deliberately: PRs cancel (a superseded run describes code that no longer exists, and the ref keys the group so PRs never cancel each other); main does NOT (a main run is the deploy trigger, and cancelling it drops that commit's deploy and leaves a hole exactly where 'was this commit ever green?' needs answering). YAML validated.</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="15" customHeight="1" s="25">
       <c r="A175" s="27" t="inlineStr">
@@ -7901,7 +8045,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H175" s="28" t="n"/>
+      <c r="H175" s="28" t="inlineStr">
+        <is>
+          <t>ATTEMPTED AND DELIBERATELY REVERTED — recorded so the next attempt does not repeat it. The finding is that the insecure-default guard keys solely on NODE_ENV === 'production'. The obvious fix is corroborating signals; both candidates are wrong here. APP_BASE_DOMAIN defaults to 'praxisls.com', so the DEFAULT is already production-shaped and 'domain is not localhost' throws on every developer machine, every unit test and every CI job — written, then caught before shipping by checking what the default actually is. DB_HOST is `postgres` in docker-compose, which is ALSO what production uses (it is a service name), so 'host is not local' never fires where it matters and does fire for a developer pointed at a remote database — exactly backwards. The audit's scenario is also narrower than it reads: the Dockerfile sets ENV NODE_ENV=production on the runtime and worker stages, so `docker compose run --rm api node …` inherits it and is already guarded; the genuine residual is a process started outside Docker with NODE_ENV unset, where the schema default is 'development'. The real fix is to stop having exploitable defaults at all — generate per-install secrets, or make the three required with no default — which is a behaviour change needing sign-off, not a cleverer sniff. A reasoned note now sits in env.js where the guard is.</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="15" customHeight="1" s="25">
       <c r="A176" s="27" t="inlineStr">
@@ -7939,7 +8087,11 @@
           <t>As reported</t>
         </is>
       </c>
-      <c r="H176" s="28" t="n"/>
+      <c r="H176" s="28" t="inlineStr">
+        <is>
+          <t>OPEN. One project with SEC-M5 and SEC-M7 — see handoff §18C. ENCRYPTION_KEY cannot be rotated without a re-encryption migration nobody has written, so in practice it can never be rotated, including after a suspected compromise.</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="15" customHeight="1" s="25">
       <c r="A177" s="27" t="inlineStr">
@@ -8011,15 +8163,19 @@
       </c>
       <c r="F178" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G178" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H178" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H178" s="28" t="inlineStr">
+        <is>
+          <t>The deploy job never checked out the repo and never recorded a SHA; it fired on CI completion and ran a script that pulled whatever main was at execution time — so for any of 44 past deploys, 'which commit did this deploy?' had no recorded answer, only an inference from timestamps. TWO halves. (1) deploy.yaml passes workflow_run.head_sha as DEPLOY_REF, so the commit that was TESTED is the commit that ships, by name. (2) deploy.sh appends to .deploy-state/deploys.log: timestamp, SHA, previous SHA, deployer, ref, status. Written at the START with 'started' and closed with the outcome, plus an EXIT trap that records 'failed(rc=N)' on any abort — a deploy that dies halfway is precisely the one needing a record, and a log that only holds successes is silent about every incident.</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="15" customHeight="1" s="25">
       <c r="A179" s="27" t="inlineStr">
@@ -8049,15 +8205,19 @@
       </c>
       <c r="F179" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G179" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H179" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H179" s="28" t="inlineStr">
+        <is>
+          <t>CHANGELOG.md added (Keep a Changelog), seeded with this remediation's user-visible changes and a 0.1.0 baseline. There was no unit of 'a release': no tags, no GitHub releases, no changelog, all three package.json frozen at 0.1.0 across 93 CI runs and 44 deploys — every commit was silently a deployment. The file documents the workflow (add a line in the same PR; at release time rename Unreleased, tag, start a fresh section) so it is maintained by the change rather than reconstructed later.</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="15" customHeight="1" s="25">
       <c r="A180" s="27" t="inlineStr">
@@ -8087,15 +8247,19 @@
       </c>
       <c r="F180" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G180" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H180" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H180" s="28" t="inlineStr">
+        <is>
+          <t>Reclassification, which is all this finding asked for. approval-wiring.test.js is now 'approval workflow — WIRING ONLY (registration, not behaviour)' with a header stating that five of six handlers are never called and that a handler registered under the right key doing entirely the wrong thing passes; individual cases renamed to say they assert registration and routing, not posting. ai-writes.test.js's first block similarly renamed to 'WIRING ONLY (an executor exists per catalogued write)'. These remain legitimate anti-regression guards — a module dropping its onApproved registration is a real, silent failure mode — the issue was bookkeeping: a reader scanning test names would reasonably count them as coverage of the approval and AI-write paths, and they are not.</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="15" customHeight="1" s="25">
       <c r="A181" s="27" t="inlineStr">
@@ -8125,15 +8289,19 @@
       </c>
       <c r="F181" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G181" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H181" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H181" s="28" t="inlineStr">
+        <is>
+          <t>CI gates the PR TITLE against conventional-commit form on pull_request events. Most commits already use prefixes, so the raw material was there — but the MERGE commits, which are the integration points a changelog is built from, carried the least information: 'Lots of changes', 'a lot', 'audit portan and opportunities board list'. A squash-merge takes its message from the PR title, so gating the title is what actually fixes the history. Permissive on scope and wording; it requires only a type prefix and six characters of description, which is the difference between a generated changelog and manual archaeology. PRs only — a push to main has no title, and TC-CI1's branch protection is what stops those.</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="15" customHeight="1" s="25">
       <c r="A182" s="27" t="inlineStr">
@@ -8163,15 +8331,19 @@
       </c>
       <c r="F182" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G182" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H182" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H182" s="28" t="inlineStr">
+        <is>
+          <t>`continue-on-error: true` replaced with a BLOCKING gate carrying a dated exception. The original reasoning was sound as far as it went — the findings are transitive uuid via exceljs/node-cron, clearing them needs a breaking exceljs major, and 'a gate everyone learns to force past is worse than one that reports honestly'. The flaw is that an exception with no expiry is indistinguishable from one nobody revisits, and these have been visible and unaddressed since the audit. npm audit --audit-level=high still, so moderates report without blocking; past EXPIRY=2026-10-31 the step FAILS, which forces the exceljs decision to be made rather than deferred again. Moving the date is allowed and is meant to come with a written reason.</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="15" customHeight="1" s="25">
       <c r="A183" s="27" t="inlineStr">
@@ -8201,15 +8373,19 @@
       </c>
       <c r="F183" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G183" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H183" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H183" s="28" t="inlineStr">
+        <is>
+          <t>`--runInBand` removed from the root `test` script and the CI Test step; measured 22.5s serial vs 7.4s parallel, identical results. Done NOW rather than later on the audit's own reasoning: while the suite is pure, any breakage from parallel workers is obviously new, whereas after database-touching tests land the cause would be ambiguous. The INTEGRATION job keeps --runInBand, where it is load-bearing — those suites share one Postgres. `test:coverage` added.</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="15" customHeight="1" s="25">
       <c r="A184" s="27" t="inlineStr">
@@ -8239,15 +8415,19 @@
       </c>
       <c r="F184" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="G184" s="28" t="inlineStr">
         <is>
-          <t>As reported</t>
-        </is>
-      </c>
-      <c r="H184" s="28" t="n"/>
+          <t>Verified in code</t>
+        </is>
+      </c>
+      <c r="H184" s="28" t="inlineStr">
+        <is>
+          <t>env-guard.test.js triggers env.js's real console.error ('Refusing to boot in production with insecure/default secrets') on every run, so every GREEN build printed a red error block — which trains people to skim past red text in CI, the precise habit you do not want on the day it is real. Silenced with a per-test spy, restored in afterEach. AND ASSERTED rather than merely swallowed: the first case now checks the guard DID print, and names JWT_ACCESS_SECRET in the output. Without that, the mock would hide a future regression where the guard stops printing and an operator loses the one line naming which secret is wrong. All 3 suites pass.</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="23.25" customHeight="1" s="25">
       <c r="A185" s="27" t="inlineStr">
@@ -9435,7 +9615,7 @@
       </c>
       <c r="D213" s="24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E213" s="24" t="inlineStr">
@@ -9445,17 +9625,17 @@
       </c>
       <c r="F213" s="24" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="G213" s="24" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Verified in code</t>
         </is>
       </c>
       <c r="H213" s="24" t="inlineStr">
         <is>
-          <t>Found 2026-08-05 while verifying the incident runbook's containment steps against the real routes. Every other write on session.routes.js carries requirePermission(MODULE, ...) — create, update, archive — and this one does not. Session ids are uuids so it is not trivially enumerable, but a session id leaks into logs and error payloads more readily than a password does, and the effect is forced logout of an arbitrary user (nuisance, or targeted denial of access to an approver mid-workflow). The sibling route /mine/revoke-all is correctly ungated because it is self-scoped.</t>
+          <t>WITHDRAWN 2026-08-05 — the finding was wrong, and how it was reached matters more than the finding. session.service.js kill() enforces exactly the right rule: `isSelf` always allowed, is_ceo allowed, otherwise identityCache.getGrants(MOD-68) must return can_update, else 403 PERMISSION_DENIED. The ROUTE is ungated on purpose and says so on the line above it — '/mine and /:id/kill are self-scoped (no MOD-68 grant needed for your own)' — because a requirePermission there would stop a user ending their own session, which is the whole point. I filed this after reading session.routes.js and never opening session.service.js: I judged a control by where I expected it to live rather than by what it does, which is the same mistake this remediation keeps documenting in other people's code. Left in the register rather than deleted, because a withdrawn finding is evidence about the review and deleting it would hide that. It also strengthens API-F23: this is precisely a self-scoped route whose authorisation is real, enforced one layer down, and invisible at the route — which is why the tier needs declaring.</t>
         </is>
       </c>
     </row>
